--- a/data_lake/datos_diarios_preliminares/dt=2026-10-18/temperaturamed.xlsx
+++ b/data_lake/datos_diarios_preliminares/dt=2026-10-18/temperaturamed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="O:\Mi unidad\OSPA\01. Tematicas\05. Datos Hidrometeorologicos\01. Productos\02.Tablas\temporales\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{599B57B4-64CA-4090-B2B3-429CBF1A9C27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2191F59D-0E44-4004-BBD5-0A06F50CF682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="729" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,6 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">DHIME!$A$1:$S$159</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Temperatura!$A$4:$AS$212</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">Temperatura!$B$4:$R$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -6354,8 +6353,8 @@
     <col min="43" max="43" width="20.7109375" style="53" customWidth="1"/>
     <col min="44" max="44" width="24.85546875" style="69" customWidth="1"/>
     <col min="45" max="45" width="13.28515625" style="70" bestFit="1" customWidth="1"/>
-    <col min="46" max="194" width="32.42578125" style="50" customWidth="1"/>
-    <col min="195" max="16384" width="32.42578125" style="50"/>
+    <col min="46" max="195" width="32.42578125" style="50" customWidth="1"/>
+    <col min="196" max="16384" width="32.42578125" style="50"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:45" x14ac:dyDescent="0.2">
@@ -6797,7 +6796,9 @@
       <c r="Z6" s="56">
         <v>29.5</v>
       </c>
-      <c r="AA6" s="56"/>
+      <c r="AA6" s="56">
+        <v>27.8</v>
+      </c>
       <c r="AB6" s="56"/>
       <c r="AC6" s="56"/>
       <c r="AD6" s="56"/>
@@ -6814,11 +6815,11 @@
       <c r="AO6" s="56"/>
       <c r="AP6" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ6" s="71">
         <f t="shared" si="1"/>
-        <v>29.012500000000003</v>
+        <v>28.941176470588239</v>
       </c>
       <c r="AR6" s="71">
         <f>IFERROR(VLOOKUP(A6,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6826,7 +6827,7 @@
       </c>
       <c r="AS6" s="71">
         <f t="shared" si="2"/>
-        <v>1.2828706093190014</v>
+        <v>1.2115470799072376</v>
       </c>
     </row>
     <row r="7" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -6908,7 +6909,9 @@
       <c r="Z7" s="56">
         <v>30.5</v>
       </c>
-      <c r="AA7" s="56"/>
+      <c r="AA7" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AB7" s="56"/>
       <c r="AC7" s="56"/>
       <c r="AD7" s="56"/>
@@ -6925,11 +6928,11 @@
       <c r="AO7" s="56"/>
       <c r="AP7" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ7" s="71">
         <f t="shared" si="1"/>
-        <v>29.949999999999996</v>
+        <v>29.958823529411763</v>
       </c>
       <c r="AR7" s="71">
         <f>IFERROR(VLOOKUP(A7,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -6937,7 +6940,7 @@
       </c>
       <c r="AS7" s="71">
         <f t="shared" si="2"/>
-        <v>1.7708828930483769</v>
+        <v>1.7797064224601442</v>
       </c>
     </row>
     <row r="8" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7019,7 +7022,9 @@
       <c r="Z8" s="56">
         <v>30.7</v>
       </c>
-      <c r="AA8" s="56"/>
+      <c r="AA8" s="56">
+        <v>30.1</v>
+      </c>
       <c r="AB8" s="56"/>
       <c r="AC8" s="56"/>
       <c r="AD8" s="56"/>
@@ -7036,11 +7041,11 @@
       <c r="AO8" s="56"/>
       <c r="AP8" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ8" s="71">
         <f t="shared" si="1"/>
-        <v>29.699999999999996</v>
+        <v>29.723529411764702</v>
       </c>
       <c r="AR8" s="71">
         <f>IFERROR(VLOOKUP(A8,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7048,7 +7053,7 @@
       </c>
       <c r="AS8" s="71">
         <f t="shared" si="2"/>
-        <v>1.4134663355196651</v>
+        <v>1.4369957472843709</v>
       </c>
     </row>
     <row r="9" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7130,7 +7135,9 @@
       <c r="Z9" s="56">
         <v>31.2</v>
       </c>
-      <c r="AA9" s="56"/>
+      <c r="AA9" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AB9" s="56"/>
       <c r="AC9" s="56"/>
       <c r="AD9" s="56"/>
@@ -7147,11 +7154,11 @@
       <c r="AO9" s="56"/>
       <c r="AP9" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ9" s="71">
         <f t="shared" si="1"/>
-        <v>29.337499999999999</v>
+        <v>29.305882352941175</v>
       </c>
       <c r="AR9" s="71">
         <f>IFERROR(VLOOKUP(A9,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7159,7 +7166,7 @@
       </c>
       <c r="AS9" s="71">
         <f t="shared" si="2"/>
-        <v>0.23365143369179719</v>
+        <v>0.202033786632974</v>
       </c>
     </row>
     <row r="10" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7237,7 +7244,9 @@
       <c r="Z10" s="56">
         <v>31</v>
       </c>
-      <c r="AA10" s="56"/>
+      <c r="AA10" s="56">
+        <v>31.1</v>
+      </c>
       <c r="AB10" s="56"/>
       <c r="AC10" s="56"/>
       <c r="AD10" s="56"/>
@@ -7254,19 +7263,19 @@
       <c r="AO10" s="56"/>
       <c r="AP10" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ10" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ10" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>30.133333333333333</v>
       </c>
       <c r="AR10" s="71">
         <f>IFERROR(VLOOKUP(A10,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.122698839392388</v>
       </c>
-      <c r="AS10" s="71" t="str">
+      <c r="AS10" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>2.0106344939409446</v>
       </c>
     </row>
     <row r="11" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7348,7 +7357,9 @@
       <c r="Z11" s="56">
         <v>31.6</v>
       </c>
-      <c r="AA11" s="56"/>
+      <c r="AA11" s="56">
+        <v>27.6</v>
+      </c>
       <c r="AB11" s="56"/>
       <c r="AC11" s="56"/>
       <c r="AD11" s="56"/>
@@ -7365,11 +7376,11 @@
       <c r="AO11" s="56"/>
       <c r="AP11" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" s="71">
         <f t="shared" si="1"/>
-        <v>29.28125</v>
+        <v>29.182352941176472</v>
       </c>
       <c r="AR11" s="71">
         <f>IFERROR(VLOOKUP(A11,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7377,7 +7388,7 @@
       </c>
       <c r="AS11" s="71">
         <f t="shared" si="2"/>
-        <v>1.5715132414628386</v>
+        <v>1.4726161826393103</v>
       </c>
     </row>
     <row r="12" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7457,7 +7468,9 @@
       <c r="Z12" s="56">
         <v>28.9</v>
       </c>
-      <c r="AA12" s="56"/>
+      <c r="AA12" s="56">
+        <v>26.5</v>
+      </c>
       <c r="AB12" s="56"/>
       <c r="AC12" s="56"/>
       <c r="AD12" s="56"/>
@@ -7474,11 +7487,11 @@
       <c r="AO12" s="56"/>
       <c r="AP12" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ12" s="71">
         <f t="shared" si="1"/>
-        <v>29.033333333333335</v>
+        <v>28.875</v>
       </c>
       <c r="AR12" s="71">
         <f>IFERROR(VLOOKUP(A12,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7486,7 +7499,7 @@
       </c>
       <c r="AS12" s="71">
         <f t="shared" si="2"/>
-        <v>1.4753364810219765</v>
+        <v>1.3170031476886415</v>
       </c>
     </row>
     <row r="13" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7568,7 +7581,9 @@
       <c r="Z13" s="56">
         <v>29.4</v>
       </c>
-      <c r="AA13" s="56"/>
+      <c r="AA13" s="56">
+        <v>27.7</v>
+      </c>
       <c r="AB13" s="56"/>
       <c r="AC13" s="56"/>
       <c r="AD13" s="56"/>
@@ -7585,11 +7600,11 @@
       <c r="AO13" s="56"/>
       <c r="AP13" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ13" s="71">
         <f t="shared" si="1"/>
-        <v>28.40625</v>
+        <v>28.36470588235294</v>
       </c>
       <c r="AR13" s="71">
         <f>IFERROR(VLOOKUP(A13,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7597,7 +7612,7 @@
       </c>
       <c r="AS13" s="71">
         <f t="shared" si="2"/>
-        <v>1.0236155913978813</v>
+        <v>0.98207147375082116</v>
       </c>
     </row>
     <row r="14" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7679,7 +7694,9 @@
       <c r="Z14" s="56">
         <v>23.9</v>
       </c>
-      <c r="AA14" s="56"/>
+      <c r="AA14" s="56">
+        <v>23.7</v>
+      </c>
       <c r="AB14" s="56"/>
       <c r="AC14" s="56"/>
       <c r="AD14" s="56"/>
@@ -7696,11 +7713,11 @@
       <c r="AO14" s="56"/>
       <c r="AP14" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ14" s="71">
         <f t="shared" si="1"/>
-        <v>23.224999999999998</v>
+        <v>23.252941176470586</v>
       </c>
       <c r="AR14" s="71">
         <f>IFERROR(VLOOKUP(A14,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7708,7 +7725,7 @@
       </c>
       <c r="AS14" s="71">
         <f t="shared" si="2"/>
-        <v>1.9659521392585972</v>
+        <v>1.9938933157291849</v>
       </c>
     </row>
     <row r="15" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7790,7 +7807,9 @@
       <c r="Z15" s="56">
         <v>31.6</v>
       </c>
-      <c r="AA15" s="56"/>
+      <c r="AA15" s="56">
+        <v>30.3</v>
+      </c>
       <c r="AB15" s="56"/>
       <c r="AC15" s="56"/>
       <c r="AD15" s="56"/>
@@ -7807,11 +7826,11 @@
       <c r="AO15" s="56"/>
       <c r="AP15" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ15" s="71">
         <f t="shared" si="1"/>
-        <v>29.706250000000001</v>
+        <v>29.741176470588236</v>
       </c>
       <c r="AR15" s="71">
         <f>IFERROR(VLOOKUP(A15,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7819,7 +7838,7 @@
       </c>
       <c r="AS15" s="71">
         <f t="shared" si="2"/>
-        <v>2.0332027649769699</v>
+        <v>2.0681292355652054</v>
       </c>
     </row>
     <row r="16" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -7901,7 +7920,9 @@
       <c r="Z16" s="56">
         <v>28.7</v>
       </c>
-      <c r="AA16" s="56"/>
+      <c r="AA16" s="56">
+        <v>28.5</v>
+      </c>
       <c r="AB16" s="56"/>
       <c r="AC16" s="56"/>
       <c r="AD16" s="56"/>
@@ -7918,11 +7939,11 @@
       <c r="AO16" s="56"/>
       <c r="AP16" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ16" s="71">
         <f t="shared" si="1"/>
-        <v>27.918749999999999</v>
+        <v>27.952941176470588</v>
       </c>
       <c r="AR16" s="71">
         <f>IFERROR(VLOOKUP(A16,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -7930,7 +7951,7 @@
       </c>
       <c r="AS16" s="71">
         <f t="shared" si="2"/>
-        <v>0.71048132759657889</v>
+        <v>0.74467250406716801</v>
       </c>
     </row>
     <row r="17" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8012,7 +8033,9 @@
       <c r="Z17" s="56">
         <v>21.7</v>
       </c>
-      <c r="AA17" s="56"/>
+      <c r="AA17" s="56">
+        <v>24.1</v>
+      </c>
       <c r="AB17" s="56"/>
       <c r="AC17" s="56"/>
       <c r="AD17" s="56"/>
@@ -8029,11 +8052,11 @@
       <c r="AO17" s="56"/>
       <c r="AP17" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ17" s="71">
         <f t="shared" si="1"/>
-        <v>22.881249999999998</v>
+        <v>22.952941176470588</v>
       </c>
       <c r="AR17" s="71">
         <f>IFERROR(VLOOKUP(A17,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8041,7 +8064,7 @@
       </c>
       <c r="AS17" s="71">
         <f t="shared" si="2"/>
-        <v>0.67533787541713863</v>
+        <v>0.74702905188772917</v>
       </c>
     </row>
     <row r="18" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8123,7 +8146,9 @@
       <c r="Z18" s="56">
         <v>17.600000000000001</v>
       </c>
-      <c r="AA18" s="56"/>
+      <c r="AA18" s="56">
+        <v>18.5</v>
+      </c>
       <c r="AB18" s="56"/>
       <c r="AC18" s="56"/>
       <c r="AD18" s="56"/>
@@ -8140,11 +8165,11 @@
       <c r="AO18" s="56"/>
       <c r="AP18" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ18" s="71">
         <f t="shared" si="1"/>
-        <v>18.331250000000001</v>
+        <v>18.341176470588238</v>
       </c>
       <c r="AR18" s="71">
         <f>IFERROR(VLOOKUP(A18,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8152,7 +8177,7 @@
       </c>
       <c r="AS18" s="71">
         <f t="shared" si="2"/>
-        <v>1.62891709521584</v>
+        <v>1.638843565804077</v>
       </c>
     </row>
     <row r="19" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8234,7 +8259,9 @@
       <c r="Z19" s="56">
         <v>22</v>
       </c>
-      <c r="AA19" s="56"/>
+      <c r="AA19" s="56">
+        <v>23.3</v>
+      </c>
       <c r="AB19" s="56"/>
       <c r="AC19" s="56"/>
       <c r="AD19" s="56"/>
@@ -8251,11 +8278,11 @@
       <c r="AO19" s="56"/>
       <c r="AP19" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ19" s="71">
         <f t="shared" si="1"/>
-        <v>22.75</v>
+        <v>22.78235294117647</v>
       </c>
       <c r="AR19" s="71">
         <f>IFERROR(VLOOKUP(A19,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8263,7 +8290,7 @@
       </c>
       <c r="AS19" s="71">
         <f t="shared" si="2"/>
-        <v>1.4720766129032299</v>
+        <v>1.5044295540796995</v>
       </c>
     </row>
     <row r="20" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8345,7 +8372,9 @@
       <c r="Z20" s="56">
         <v>23.1</v>
       </c>
-      <c r="AA20" s="56"/>
+      <c r="AA20" s="56">
+        <v>22.6</v>
+      </c>
       <c r="AB20" s="56"/>
       <c r="AC20" s="56"/>
       <c r="AD20" s="56"/>
@@ -8362,11 +8391,11 @@
       <c r="AO20" s="56"/>
       <c r="AP20" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ20" s="71">
         <f t="shared" si="1"/>
-        <v>22.974999999999998</v>
+        <v>22.952941176470588</v>
       </c>
       <c r="AR20" s="71">
         <f>IFERROR(VLOOKUP(A20,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8374,7 +8403,7 @@
       </c>
       <c r="AS20" s="71">
         <f t="shared" si="2"/>
-        <v>1.3674242424242493</v>
+        <v>1.3453654188948398</v>
       </c>
     </row>
     <row r="21" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8456,7 +8485,9 @@
       <c r="Z21" s="56">
         <v>26.1</v>
       </c>
-      <c r="AA21" s="56"/>
+      <c r="AA21" s="56">
+        <v>26.8</v>
+      </c>
       <c r="AB21" s="56"/>
       <c r="AC21" s="56"/>
       <c r="AD21" s="56"/>
@@ -8473,11 +8504,11 @@
       <c r="AO21" s="56"/>
       <c r="AP21" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ21" s="71">
         <f t="shared" si="1"/>
-        <v>24.993749999999999</v>
+        <v>25.099999999999998</v>
       </c>
       <c r="AR21" s="71">
         <f>IFERROR(VLOOKUP(A21,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8485,7 +8516,7 @@
       </c>
       <c r="AS21" s="71">
         <f t="shared" si="2"/>
-        <v>1.3390596032628892</v>
+        <v>1.4453096032628885</v>
       </c>
     </row>
     <row r="22" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8567,7 +8598,9 @@
       <c r="Z22" s="56">
         <v>16.100000000000001</v>
       </c>
-      <c r="AA22" s="56"/>
+      <c r="AA22" s="56">
+        <v>16.7</v>
+      </c>
       <c r="AB22" s="56"/>
       <c r="AC22" s="56"/>
       <c r="AD22" s="56"/>
@@ -8584,11 +8617,11 @@
       <c r="AO22" s="56"/>
       <c r="AP22" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ22" s="71">
         <f t="shared" si="1"/>
-        <v>16.031250000000004</v>
+        <v>16.070588235294121</v>
       </c>
       <c r="AR22" s="71">
         <f>IFERROR(VLOOKUP(A22,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8596,7 +8629,7 @@
       </c>
       <c r="AS22" s="71">
         <f t="shared" si="2"/>
-        <v>2.2817818740399538</v>
+        <v>2.3211201093340712</v>
       </c>
     </row>
     <row r="23" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8678,7 +8711,9 @@
       <c r="Z23" s="56">
         <v>25</v>
       </c>
-      <c r="AA23" s="56"/>
+      <c r="AA23" s="56">
+        <v>26.3</v>
+      </c>
       <c r="AB23" s="56"/>
       <c r="AC23" s="56"/>
       <c r="AD23" s="56"/>
@@ -8695,11 +8730,11 @@
       <c r="AO23" s="56"/>
       <c r="AP23" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ23" s="71">
         <f t="shared" si="1"/>
-        <v>24.462499999999999</v>
+        <v>24.570588235294117</v>
       </c>
       <c r="AR23" s="71" t="str">
         <f>IFERROR(VLOOKUP(A23,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8789,7 +8824,9 @@
       <c r="Z24" s="56">
         <v>31.6</v>
       </c>
-      <c r="AA24" s="56"/>
+      <c r="AA24" s="56">
+        <v>30.8</v>
+      </c>
       <c r="AB24" s="56"/>
       <c r="AC24" s="56"/>
       <c r="AD24" s="56"/>
@@ -8806,11 +8843,11 @@
       <c r="AO24" s="56"/>
       <c r="AP24" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ24" s="71">
         <f t="shared" si="1"/>
-        <v>29.737500000000001</v>
+        <v>29.8</v>
       </c>
       <c r="AR24" s="71">
         <f>IFERROR(VLOOKUP(A24,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8818,7 +8855,7 @@
       </c>
       <c r="AS24" s="71">
         <f t="shared" si="2"/>
-        <v>1.4836860812425421</v>
+        <v>1.5461860812425421</v>
       </c>
     </row>
     <row r="25" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -8900,7 +8937,9 @@
       <c r="Z25" s="56">
         <v>19.8</v>
       </c>
-      <c r="AA25" s="56"/>
+      <c r="AA25" s="56">
+        <v>20.5</v>
+      </c>
       <c r="AB25" s="56"/>
       <c r="AC25" s="56"/>
       <c r="AD25" s="56"/>
@@ -8917,11 +8956,11 @@
       <c r="AO25" s="56"/>
       <c r="AP25" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ25" s="71">
         <f t="shared" si="1"/>
-        <v>20.2</v>
+        <v>20.21764705882353</v>
       </c>
       <c r="AR25" s="71">
         <f>IFERROR(VLOOKUP(A25,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -8929,7 +8968,7 @@
       </c>
       <c r="AS25" s="71">
         <f t="shared" si="2"/>
-        <v>1.2138960905492304</v>
+        <v>1.2315431493727615</v>
       </c>
     </row>
     <row r="26" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9011,7 +9050,9 @@
       <c r="Z26" s="56">
         <v>12</v>
       </c>
-      <c r="AA26" s="56"/>
+      <c r="AA26" s="56">
+        <v>11.9</v>
+      </c>
       <c r="AB26" s="56"/>
       <c r="AC26" s="56"/>
       <c r="AD26" s="56"/>
@@ -9028,11 +9069,11 @@
       <c r="AO26" s="56"/>
       <c r="AP26" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ26" s="71">
         <f t="shared" si="1"/>
-        <v>12.85</v>
+        <v>12.794117647058824</v>
       </c>
       <c r="AR26" s="71">
         <f>IFERROR(VLOOKUP(A26,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9040,7 +9081,7 @@
       </c>
       <c r="AS26" s="71">
         <f t="shared" si="2"/>
-        <v>1.4878456221198491</v>
+        <v>1.4319632691786737</v>
       </c>
     </row>
     <row r="27" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9122,7 +9163,9 @@
       <c r="Z27" s="56">
         <v>24.3</v>
       </c>
-      <c r="AA27" s="56"/>
+      <c r="AA27" s="56">
+        <v>27.9</v>
+      </c>
       <c r="AB27" s="56"/>
       <c r="AC27" s="56"/>
       <c r="AD27" s="56"/>
@@ -9139,11 +9182,11 @@
       <c r="AO27" s="56"/>
       <c r="AP27" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ27" s="71">
         <f t="shared" si="1"/>
-        <v>27.443750000000001</v>
+        <v>27.470588235294116</v>
       </c>
       <c r="AR27" s="71">
         <f>IFERROR(VLOOKUP(A27,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9151,7 +9194,7 @@
       </c>
       <c r="AS27" s="71">
         <f t="shared" si="2"/>
-        <v>1.0152600111234804</v>
+        <v>1.042098246417595</v>
       </c>
     </row>
     <row r="28" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9233,7 +9276,9 @@
       <c r="Z28" s="56">
         <v>29.3</v>
       </c>
-      <c r="AA28" s="56"/>
+      <c r="AA28" s="56">
+        <v>28.8</v>
+      </c>
       <c r="AB28" s="56"/>
       <c r="AC28" s="56"/>
       <c r="AD28" s="56"/>
@@ -9250,11 +9295,11 @@
       <c r="AO28" s="56"/>
       <c r="AP28" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ28" s="71">
         <f t="shared" si="1"/>
-        <v>28.743749999999999</v>
+        <v>28.747058823529411</v>
       </c>
       <c r="AR28" s="71">
         <f>IFERROR(VLOOKUP(A28,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9262,7 +9307,7 @@
       </c>
       <c r="AS28" s="71">
         <f t="shared" si="2"/>
-        <v>1.8859555564213188</v>
+        <v>1.8892643799507312</v>
       </c>
     </row>
     <row r="29" spans="1:45" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -9344,7 +9389,9 @@
       <c r="Z29" s="56">
         <v>30</v>
       </c>
-      <c r="AA29" s="56"/>
+      <c r="AA29" s="56">
+        <v>30.2</v>
+      </c>
       <c r="AB29" s="56"/>
       <c r="AC29" s="56"/>
       <c r="AD29" s="56"/>
@@ -9361,11 +9408,11 @@
       <c r="AO29" s="56"/>
       <c r="AP29" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ29" s="71">
         <f t="shared" si="1"/>
-        <v>29.40625</v>
+        <v>29.452941176470588</v>
       </c>
       <c r="AR29" s="71">
         <f>IFERROR(VLOOKUP(A29,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9373,7 +9420,7 @@
       </c>
       <c r="AS29" s="71">
         <f t="shared" si="2"/>
-        <v>1.0350597886540989</v>
+        <v>1.0817509651246873</v>
       </c>
     </row>
     <row r="30" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9455,7 +9502,9 @@
       <c r="Z30" s="56">
         <v>29.5</v>
       </c>
-      <c r="AA30" s="56"/>
+      <c r="AA30" s="56">
+        <v>27.2</v>
+      </c>
       <c r="AB30" s="56"/>
       <c r="AC30" s="56"/>
       <c r="AD30" s="56"/>
@@ -9472,11 +9521,11 @@
       <c r="AO30" s="56"/>
       <c r="AP30" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ30" s="71">
         <f t="shared" si="1"/>
-        <v>26.900000000000002</v>
+        <v>26.91764705882353</v>
       </c>
       <c r="AR30" s="71">
         <f>IFERROR(VLOOKUP(A30,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9484,7 +9533,7 @@
       </c>
       <c r="AS30" s="71">
         <f t="shared" si="2"/>
-        <v>1.0271672640382725</v>
+        <v>1.0448143228618001</v>
       </c>
     </row>
     <row r="31" spans="1:45" ht="16.149999999999999" customHeight="1" x14ac:dyDescent="0.2">
@@ -9566,7 +9615,9 @@
       <c r="Z31" s="98">
         <v>28.9</v>
       </c>
-      <c r="AA31" s="98"/>
+      <c r="AA31" s="98">
+        <v>27.2</v>
+      </c>
       <c r="AB31" s="98"/>
       <c r="AC31" s="98"/>
       <c r="AD31" s="98"/>
@@ -9583,11 +9634,11 @@
       <c r="AO31" s="98"/>
       <c r="AP31" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ31" s="71">
         <f t="shared" si="1"/>
-        <v>28.281249999999996</v>
+        <v>28.217647058823527</v>
       </c>
       <c r="AR31" s="71">
         <f>IFERROR(VLOOKUP(A31,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9595,7 +9646,7 @@
       </c>
       <c r="AS31" s="71">
         <f t="shared" si="2"/>
-        <v>1.6867262246117072</v>
+        <v>1.6231232834352376</v>
       </c>
     </row>
     <row r="32" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9677,7 +9728,9 @@
       <c r="Z32" s="56">
         <v>20.533333333333331</v>
       </c>
-      <c r="AA32" s="56"/>
+      <c r="AA32" s="56">
+        <v>19.333333333333329</v>
+      </c>
       <c r="AB32" s="56"/>
       <c r="AC32" s="56"/>
       <c r="AD32" s="56"/>
@@ -9694,11 +9747,11 @@
       <c r="AO32" s="56"/>
       <c r="AP32" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ32" s="71">
         <f t="shared" si="1"/>
-        <v>19.764583333333327</v>
+        <v>19.739215686274502</v>
       </c>
       <c r="AR32" s="71">
         <f>IFERROR(VLOOKUP(A32,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9706,7 +9759,7 @@
       </c>
       <c r="AS32" s="71">
         <f t="shared" si="2"/>
-        <v>2.5101454382327262</v>
+        <v>2.4847777911739009</v>
       </c>
     </row>
     <row r="33" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9788,7 +9841,9 @@
       <c r="Z33" s="56">
         <v>28.4</v>
       </c>
-      <c r="AA33" s="56"/>
+      <c r="AA33" s="56">
+        <v>28.4</v>
+      </c>
       <c r="AB33" s="56"/>
       <c r="AC33" s="56"/>
       <c r="AD33" s="56"/>
@@ -9805,11 +9860,11 @@
       <c r="AO33" s="56"/>
       <c r="AP33" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ33" s="71">
         <f t="shared" si="1"/>
-        <v>27.518750000000001</v>
+        <v>27.570588235294117</v>
       </c>
       <c r="AR33" s="71">
         <f>IFERROR(VLOOKUP(A33,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9817,7 +9872,7 @@
       </c>
       <c r="AS33" s="71">
         <f t="shared" si="2"/>
-        <v>1.0387238367492202</v>
+        <v>1.0905620720433369</v>
       </c>
     </row>
     <row r="34" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -9899,7 +9954,9 @@
       <c r="Z34" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="AA34" s="56"/>
+      <c r="AA34" s="56">
+        <v>21.06666666666667</v>
+      </c>
       <c r="AB34" s="56"/>
       <c r="AC34" s="56"/>
       <c r="AD34" s="56"/>
@@ -9916,11 +9973,11 @@
       <c r="AO34" s="56"/>
       <c r="AP34" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ34" s="71">
         <f t="shared" si="1"/>
-        <v>20.574999999999996</v>
+        <v>20.603921568627445</v>
       </c>
       <c r="AR34" s="71">
         <f>IFERROR(VLOOKUP(A34,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -9928,7 +9985,7 @@
       </c>
       <c r="AS34" s="71">
         <f t="shared" si="2"/>
-        <v>1.1175386231615647</v>
+        <v>1.1464601917890143</v>
       </c>
     </row>
     <row r="35" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10010,7 +10067,9 @@
       <c r="Z35" s="56">
         <v>23.5</v>
       </c>
-      <c r="AA35" s="56"/>
+      <c r="AA35" s="56">
+        <v>25.4</v>
+      </c>
       <c r="AB35" s="56"/>
       <c r="AC35" s="56"/>
       <c r="AD35" s="56"/>
@@ -10027,11 +10086,11 @@
       <c r="AO35" s="56"/>
       <c r="AP35" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ35" s="71">
         <f t="shared" si="1"/>
-        <v>24.006250000000001</v>
+        <v>24.088235294117649</v>
       </c>
       <c r="AR35" s="71">
         <f>IFERROR(VLOOKUP(A35,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10039,7 +10098,7 @@
       </c>
       <c r="AS35" s="71">
         <f t="shared" si="2"/>
-        <v>0.48134026835202093</v>
+        <v>0.56332556246966803</v>
       </c>
     </row>
     <row r="36" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10121,7 +10180,9 @@
       <c r="Z36" s="56">
         <v>17.350000000000001</v>
       </c>
-      <c r="AA36" s="56"/>
+      <c r="AA36" s="56">
+        <v>19.399999999999999</v>
+      </c>
       <c r="AB36" s="56"/>
       <c r="AC36" s="56"/>
       <c r="AD36" s="56"/>
@@ -10138,11 +10199,11 @@
       <c r="AO36" s="56"/>
       <c r="AP36" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ36" s="71">
         <f t="shared" si="1"/>
-        <v>19.059375000000003</v>
+        <v>19.079411764705885</v>
       </c>
       <c r="AR36" s="71">
         <f>IFERROR(VLOOKUP(A36,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10150,7 +10211,7 @@
       </c>
       <c r="AS36" s="71">
         <f t="shared" si="2"/>
-        <v>1.0925259954371214</v>
+        <v>1.1125627601430033</v>
       </c>
     </row>
     <row r="37" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10232,7 +10293,9 @@
       <c r="Z37" s="56">
         <v>25.05</v>
       </c>
-      <c r="AA37" s="56"/>
+      <c r="AA37" s="56">
+        <v>27.4</v>
+      </c>
       <c r="AB37" s="56"/>
       <c r="AC37" s="56"/>
       <c r="AD37" s="56"/>
@@ -10249,11 +10312,11 @@
       <c r="AO37" s="56"/>
       <c r="AP37" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ37" s="71">
         <f t="shared" si="1"/>
-        <v>26.559375000000003</v>
+        <v>26.608823529411765</v>
       </c>
       <c r="AR37" s="71">
         <f>IFERROR(VLOOKUP(A37,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10261,7 +10324,7 @@
       </c>
       <c r="AS37" s="71">
         <f t="shared" si="2"/>
-        <v>1.0749719081887612</v>
+        <v>1.1244204376005236</v>
       </c>
     </row>
     <row r="38" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10343,7 +10406,9 @@
       <c r="Z38" s="56">
         <v>14.9</v>
       </c>
-      <c r="AA38" s="56"/>
+      <c r="AA38" s="56">
+        <v>14.75</v>
+      </c>
       <c r="AB38" s="56"/>
       <c r="AC38" s="56"/>
       <c r="AD38" s="56"/>
@@ -10360,11 +10425,11 @@
       <c r="AO38" s="56"/>
       <c r="AP38" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ38" s="71">
         <f t="shared" si="1"/>
-        <v>15.403125000000001</v>
+        <v>15.364705882352943</v>
       </c>
       <c r="AR38" s="71">
         <f>IFERROR(VLOOKUP(A38,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10372,7 +10437,7 @@
       </c>
       <c r="AS38" s="71">
         <f t="shared" si="2"/>
-        <v>0.64190230105763035</v>
+        <v>0.60348318341057272</v>
       </c>
     </row>
     <row r="39" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10454,7 +10519,9 @@
       <c r="Z39" s="56">
         <v>20.333333333333329</v>
       </c>
-      <c r="AA39" s="56"/>
+      <c r="AA39" s="56">
+        <v>21.533333333333331</v>
+      </c>
       <c r="AB39" s="56"/>
       <c r="AC39" s="56"/>
       <c r="AD39" s="56"/>
@@ -10471,11 +10538,11 @@
       <c r="AO39" s="56"/>
       <c r="AP39" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ39" s="71">
         <f t="shared" si="1"/>
-        <v>20.829166666666666</v>
+        <v>20.870588235294115</v>
       </c>
       <c r="AR39" s="71" t="str">
         <f>IFERROR(VLOOKUP(A39,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10653,7 +10720,9 @@
       <c r="Y41" s="56">
         <v>18.399999999999999</v>
       </c>
-      <c r="Z41" s="56"/>
+      <c r="Z41" s="56">
+        <v>19.133333333333329</v>
+      </c>
       <c r="AA41" s="56"/>
       <c r="AB41" s="56"/>
       <c r="AC41" s="56"/>
@@ -10671,11 +10740,11 @@
       <c r="AO41" s="56"/>
       <c r="AP41" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ41" s="71">
         <f t="shared" si="1"/>
-        <v>18.404444444444444</v>
+        <v>18.45</v>
       </c>
       <c r="AR41" s="71">
         <f>IFERROR(VLOOKUP(A41,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10683,7 +10752,7 @@
       </c>
       <c r="AS41" s="71">
         <f t="shared" si="2"/>
-        <v>0.59491851072674251</v>
+        <v>0.64047406628229808</v>
       </c>
     </row>
     <row r="42" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10763,7 +10832,9 @@
       <c r="Z42" s="56">
         <v>29</v>
       </c>
-      <c r="AA42" s="56"/>
+      <c r="AA42" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AB42" s="56"/>
       <c r="AC42" s="56"/>
       <c r="AD42" s="56"/>
@@ -10780,11 +10851,11 @@
       <c r="AO42" s="56"/>
       <c r="AP42" s="58">
         <f t="shared" si="0"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ42" s="71">
         <f t="shared" si="1"/>
-        <v>27.95333333333333</v>
+        <v>27.912499999999998</v>
       </c>
       <c r="AR42" s="71">
         <f>IFERROR(VLOOKUP(A42,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10792,7 +10863,7 @@
       </c>
       <c r="AS42" s="71">
         <f t="shared" si="2"/>
-        <v>0.77930406212664849</v>
+        <v>0.73847072879331677</v>
       </c>
     </row>
     <row r="43" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -10874,7 +10945,9 @@
       <c r="Z43" s="56">
         <v>30.5</v>
       </c>
-      <c r="AA43" s="56"/>
+      <c r="AA43" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AB43" s="56"/>
       <c r="AC43" s="56"/>
       <c r="AD43" s="56"/>
@@ -10891,11 +10964,11 @@
       <c r="AO43" s="56"/>
       <c r="AP43" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ43" s="71">
         <f t="shared" si="1"/>
-        <v>28.771874999999998</v>
+        <v>28.705882352941174</v>
       </c>
       <c r="AR43" s="71" t="str">
         <f>IFERROR(VLOOKUP(A43,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -10985,7 +11058,9 @@
       <c r="Z44" s="56">
         <v>28.45</v>
       </c>
-      <c r="AA44" s="56"/>
+      <c r="AA44" s="56">
+        <v>27.274999999999999</v>
+      </c>
       <c r="AB44" s="56"/>
       <c r="AC44" s="56"/>
       <c r="AD44" s="56"/>
@@ -11002,11 +11077,11 @@
       <c r="AO44" s="56"/>
       <c r="AP44" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ44" s="71">
         <f t="shared" si="1"/>
-        <v>27.96875</v>
+        <v>27.927941176470586</v>
       </c>
       <c r="AR44" s="71">
         <f>IFERROR(VLOOKUP(A44,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11014,7 +11089,7 @@
       </c>
       <c r="AS44" s="71">
         <f t="shared" si="2"/>
-        <v>0.74052512050426955</v>
+        <v>0.69971629697485582</v>
       </c>
     </row>
     <row r="45" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11096,7 +11171,9 @@
       <c r="Z45" s="56">
         <v>28.35</v>
       </c>
-      <c r="AA45" s="56"/>
+      <c r="AA45" s="56">
+        <v>28.45</v>
+      </c>
       <c r="AB45" s="56"/>
       <c r="AC45" s="56"/>
       <c r="AD45" s="56"/>
@@ -11113,11 +11190,11 @@
       <c r="AO45" s="56"/>
       <c r="AP45" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ45" s="71">
         <f t="shared" si="1"/>
-        <v>27.796875000000004</v>
+        <v>27.835294117647063</v>
       </c>
       <c r="AR45" s="71">
         <f>IFERROR(VLOOKUP(A45,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11125,7 +11202,7 @@
       </c>
       <c r="AS45" s="71">
         <f t="shared" si="2"/>
-        <v>0.90804326934177482</v>
+        <v>0.94646238698883423</v>
       </c>
     </row>
     <row r="46" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11525,7 +11602,9 @@
       <c r="Z50" s="56">
         <v>30.3</v>
       </c>
-      <c r="AA50" s="56"/>
+      <c r="AA50" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AB50" s="56"/>
       <c r="AC50" s="56"/>
       <c r="AD50" s="56"/>
@@ -11542,11 +11621,11 @@
       <c r="AO50" s="56"/>
       <c r="AP50" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ50" s="71">
         <f t="shared" si="1"/>
-        <v>28.028125000000003</v>
+        <v>28.044117647058826</v>
       </c>
       <c r="AR50" s="71">
         <f>IFERROR(VLOOKUP(A50,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11554,7 +11633,7 @@
       </c>
       <c r="AS50" s="71">
         <f t="shared" si="2"/>
-        <v>0.83822539729741408</v>
+        <v>0.85421804435623727</v>
       </c>
     </row>
     <row r="51" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11794,7 +11873,9 @@
       <c r="Z53" s="56">
         <v>29.15</v>
       </c>
-      <c r="AA53" s="56"/>
+      <c r="AA53" s="56">
+        <v>27.3</v>
+      </c>
       <c r="AB53" s="56"/>
       <c r="AC53" s="56"/>
       <c r="AD53" s="56"/>
@@ -11811,11 +11892,11 @@
       <c r="AO53" s="56"/>
       <c r="AP53" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ53" s="71">
         <f t="shared" si="1"/>
-        <v>27.146874999999998</v>
+        <v>27.155882352941177</v>
       </c>
       <c r="AR53" s="71">
         <f>IFERROR(VLOOKUP(A53,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11823,7 +11904,7 @@
       </c>
       <c r="AS53" s="71">
         <f t="shared" si="2"/>
-        <v>0.64819618141384794</v>
+        <v>0.65720353435502687</v>
       </c>
     </row>
     <row r="54" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -11905,7 +11986,9 @@
       <c r="Z54" s="56">
         <v>30.3</v>
       </c>
-      <c r="AA54" s="56"/>
+      <c r="AA54" s="56">
+        <v>26.15</v>
+      </c>
       <c r="AB54" s="56"/>
       <c r="AC54" s="56"/>
       <c r="AD54" s="56"/>
@@ -11922,11 +12005,11 @@
       <c r="AO54" s="56"/>
       <c r="AP54" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ54" s="71">
         <f t="shared" si="1"/>
-        <v>28.603125000000002</v>
+        <v>28.458823529411767</v>
       </c>
       <c r="AR54" s="71">
         <f>IFERROR(VLOOKUP(A54,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -11934,7 +12017,7 @@
       </c>
       <c r="AS54" s="71">
         <f t="shared" si="2"/>
-        <v>0.61385171469982325</v>
+        <v>0.46955024411158774</v>
       </c>
     </row>
     <row r="55" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12358,7 +12441,9 @@
       <c r="Z59" s="56">
         <v>28.8</v>
       </c>
-      <c r="AA59" s="56"/>
+      <c r="AA59" s="56">
+        <v>29.8</v>
+      </c>
       <c r="AB59" s="56"/>
       <c r="AC59" s="99"/>
       <c r="AD59" s="56"/>
@@ -12375,11 +12460,11 @@
       <c r="AO59" s="56"/>
       <c r="AP59" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ59" s="71">
         <f t="shared" si="1"/>
-        <v>28.187500000000004</v>
+        <v>28.282352941176473</v>
       </c>
       <c r="AR59" s="71">
         <f>IFERROR(VLOOKUP(A59,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12387,7 +12472,7 @@
       </c>
       <c r="AS59" s="71">
         <f t="shared" si="2"/>
-        <v>0.97430990840986453</v>
+        <v>1.0691628495863341</v>
       </c>
     </row>
     <row r="60" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12459,7 +12544,9 @@
       <c r="Z60" s="56">
         <v>28.45</v>
       </c>
-      <c r="AA60" s="56"/>
+      <c r="AA60" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AB60" s="56"/>
       <c r="AC60" s="56"/>
       <c r="AD60" s="56"/>
@@ -12476,7 +12563,7 @@
       <c r="AO60" s="56"/>
       <c r="AP60" s="58">
         <f t="shared" si="0"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ60" s="71" t="str">
         <f t="shared" si="1"/>
@@ -12566,7 +12653,9 @@
       <c r="Z61" s="56">
         <v>26.85</v>
       </c>
-      <c r="AA61" s="56"/>
+      <c r="AA61" s="56">
+        <v>27.65</v>
+      </c>
       <c r="AB61" s="56"/>
       <c r="AC61" s="56"/>
       <c r="AD61" s="56"/>
@@ -12583,19 +12672,19 @@
       <c r="AO61" s="56"/>
       <c r="AP61" s="58">
         <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="AQ61" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ61" s="71">
         <f t="shared" si="1"/>
-        <v/>
+        <v>27.990000000000002</v>
       </c>
       <c r="AR61" s="71">
         <f>IFERROR(VLOOKUP(A61,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.804794338924129</v>
       </c>
-      <c r="AS61" s="71" t="str">
+      <c r="AS61" s="71">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1.185205661075873</v>
       </c>
     </row>
     <row r="62" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12677,7 +12766,9 @@
       <c r="Z62" s="56">
         <v>28.86666666666666</v>
       </c>
-      <c r="AA62" s="56"/>
+      <c r="AA62" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AB62" s="56"/>
       <c r="AC62" s="56"/>
       <c r="AD62" s="56"/>
@@ -12694,11 +12785,11 @@
       <c r="AO62" s="56"/>
       <c r="AP62" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ62" s="71">
         <f t="shared" si="1"/>
-        <v>27.745833333333334</v>
+        <v>27.654901960784315</v>
       </c>
       <c r="AR62" s="71">
         <f>IFERROR(VLOOKUP(A62,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12706,7 +12797,7 @@
       </c>
       <c r="AS62" s="71">
         <f t="shared" si="2"/>
-        <v>1.879328482516744</v>
+        <v>1.7883971099677254</v>
       </c>
     </row>
     <row r="63" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -12946,7 +13037,9 @@
       <c r="Z65" s="56">
         <v>26.85</v>
       </c>
-      <c r="AA65" s="56"/>
+      <c r="AA65" s="56">
+        <v>25.95</v>
+      </c>
       <c r="AB65" s="56"/>
       <c r="AC65" s="56"/>
       <c r="AD65" s="56"/>
@@ -12963,11 +13056,11 @@
       <c r="AO65" s="56"/>
       <c r="AP65" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ65" s="71">
         <f t="shared" si="1"/>
-        <v>26.875</v>
+        <v>26.820588235294117</v>
       </c>
       <c r="AR65" s="71">
         <f>IFERROR(VLOOKUP(A65,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -12975,7 +13068,7 @@
       </c>
       <c r="AS65" s="71">
         <f t="shared" si="2"/>
-        <v>0.77741575213811842</v>
+        <v>0.72300398743223582</v>
       </c>
     </row>
     <row r="66" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13057,7 +13150,9 @@
       <c r="Z66" s="56">
         <v>27.5</v>
       </c>
-      <c r="AA66" s="56"/>
+      <c r="AA66" s="56">
+        <v>26.1</v>
+      </c>
       <c r="AB66" s="56"/>
       <c r="AC66" s="56"/>
       <c r="AD66" s="56"/>
@@ -13074,11 +13169,11 @@
       <c r="AO66" s="56"/>
       <c r="AP66" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ66" s="71">
         <f t="shared" si="1"/>
-        <v>27.106249999999996</v>
+        <v>27.047058823529408</v>
       </c>
       <c r="AR66" s="71">
         <f>IFERROR(VLOOKUP(A66,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13086,7 +13181,7 @@
       </c>
       <c r="AS66" s="71">
         <f t="shared" si="2"/>
-        <v>0.91981707542344537</v>
+        <v>0.86062589895285768</v>
       </c>
     </row>
     <row r="67" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13162,7 +13257,9 @@
       <c r="Z67" s="56">
         <v>27.8</v>
       </c>
-      <c r="AA67" s="56"/>
+      <c r="AA67" s="56">
+        <v>25.75</v>
+      </c>
       <c r="AB67" s="56"/>
       <c r="AC67" s="56"/>
       <c r="AD67" s="56"/>
@@ -13179,7 +13276,7 @@
       <c r="AO67" s="56"/>
       <c r="AP67" s="58">
         <f t="shared" si="0"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ67" s="71" t="str">
         <f t="shared" si="1"/>
@@ -13273,7 +13370,9 @@
       <c r="Z68" s="56">
         <v>26.8</v>
       </c>
-      <c r="AA68" s="56"/>
+      <c r="AA68" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AB68" s="56"/>
       <c r="AC68" s="56"/>
       <c r="AD68" s="56"/>
@@ -13290,11 +13389,11 @@
       <c r="AO68" s="56"/>
       <c r="AP68" s="58">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ68" s="71">
         <f t="shared" si="1"/>
-        <v>26.196874999999999</v>
+        <v>26.138235294117646</v>
       </c>
       <c r="AR68" s="71">
         <f>IFERROR(VLOOKUP(A68,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13302,7 +13401,7 @@
       </c>
       <c r="AS68" s="71">
         <f t="shared" si="2"/>
-        <v>0.41582889179237981</v>
+        <v>0.35718918591002691</v>
       </c>
     </row>
     <row r="69" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13384,7 +13483,9 @@
       <c r="Z69" s="56">
         <v>26.55</v>
       </c>
-      <c r="AA69" s="56"/>
+      <c r="AA69" s="56">
+        <v>25.3</v>
+      </c>
       <c r="AB69" s="56"/>
       <c r="AC69" s="56"/>
       <c r="AD69" s="56"/>
@@ -13401,11 +13502,11 @@
       <c r="AO69" s="56"/>
       <c r="AP69" s="58">
         <f t="shared" ref="AP69:AP132" si="3">COUNTIF(K69:AO69,"&gt;0")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ69" s="71">
         <f t="shared" ref="AQ69:AQ132" si="4">IF(AP69&gt;14,AVERAGE(K69:AO69),"")</f>
-        <v>26.068749999999998</v>
+        <v>26.023529411764706</v>
       </c>
       <c r="AR69" s="71">
         <f>IFERROR(VLOOKUP(A69,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13413,7 +13514,7 @@
       </c>
       <c r="AS69" s="71">
         <f t="shared" ref="AS69:AS132" si="5">IF(OR(AQ69="",AR69=""),"",IFERROR(AQ69-AR69,""))</f>
-        <v>0.34026938899046755</v>
+        <v>0.29504880075517548</v>
       </c>
     </row>
     <row r="70" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13606,7 +13707,9 @@
       <c r="Z71" s="56">
         <v>28.166666666666671</v>
       </c>
-      <c r="AA71" s="56"/>
+      <c r="AA71" s="56">
+        <v>25.43333333333333</v>
+      </c>
       <c r="AB71" s="56"/>
       <c r="AC71" s="56"/>
       <c r="AD71" s="56"/>
@@ -13623,11 +13726,11 @@
       <c r="AO71" s="56"/>
       <c r="AP71" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ71" s="71">
         <f t="shared" si="4"/>
-        <v>27.562499999999996</v>
+        <v>27.437254901960781</v>
       </c>
       <c r="AR71" s="71">
         <f>IFERROR(VLOOKUP(A71,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13635,7 +13738,7 @@
       </c>
       <c r="AS71" s="71">
         <f t="shared" si="5"/>
-        <v>0.62797317141086495</v>
+        <v>0.50272807337164949</v>
       </c>
     </row>
     <row r="72" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13715,7 +13818,9 @@
       <c r="Z72" s="56">
         <v>26.5</v>
       </c>
-      <c r="AA72" s="56"/>
+      <c r="AA72" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AB72" s="56"/>
       <c r="AC72" s="56"/>
       <c r="AD72" s="56"/>
@@ -13732,11 +13837,11 @@
       <c r="AO72" s="56"/>
       <c r="AP72" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ72" s="71">
         <f t="shared" si="4"/>
-        <v>26.606666666666669</v>
+        <v>26.581250000000001</v>
       </c>
       <c r="AR72" s="71">
         <f>IFERROR(VLOOKUP(A72,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13744,7 +13849,7 @@
       </c>
       <c r="AS72" s="71">
         <f t="shared" si="5"/>
-        <v>0.76215538039697961</v>
+        <v>0.73673871373031119</v>
       </c>
     </row>
     <row r="73" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -13915,7 +14020,9 @@
       <c r="Z74" s="56">
         <v>24.15</v>
       </c>
-      <c r="AA74" s="56"/>
+      <c r="AA74" s="56">
+        <v>21.9</v>
+      </c>
       <c r="AB74" s="56"/>
       <c r="AC74" s="56"/>
       <c r="AD74" s="56"/>
@@ -13932,11 +14039,11 @@
       <c r="AO74" s="56"/>
       <c r="AP74" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ74" s="71">
         <f t="shared" si="4"/>
-        <v>22.581250000000001</v>
+        <v>22.541176470588233</v>
       </c>
       <c r="AR74" s="71">
         <f>IFERROR(VLOOKUP(A74,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -13944,7 +14051,7 @@
       </c>
       <c r="AS74" s="71">
         <f t="shared" si="5"/>
-        <v>1.3552324153958999</v>
+        <v>1.3151588859841326</v>
       </c>
     </row>
     <row r="75" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14026,7 +14133,9 @@
       <c r="Z75" s="56">
         <v>16.666666666666671</v>
       </c>
-      <c r="AA75" s="56"/>
+      <c r="AA75" s="56">
+        <v>16.13333333333334</v>
+      </c>
       <c r="AB75" s="56"/>
       <c r="AC75" s="56"/>
       <c r="AD75" s="56"/>
@@ -14043,11 +14152,11 @@
       <c r="AO75" s="56"/>
       <c r="AP75" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ75" s="71">
         <f t="shared" si="4"/>
-        <v>16.600000000000001</v>
+        <v>16.572549019607845</v>
       </c>
       <c r="AR75" s="71">
         <f>IFERROR(VLOOKUP(A75,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14055,7 +14164,7 @@
       </c>
       <c r="AS75" s="71">
         <f t="shared" si="5"/>
-        <v>0.76281046007611231</v>
+        <v>0.73535947968395554</v>
       </c>
     </row>
     <row r="76" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14137,7 +14246,9 @@
       <c r="Z76" s="56">
         <v>22</v>
       </c>
-      <c r="AA76" s="56"/>
+      <c r="AA76" s="56">
+        <v>20.85</v>
+      </c>
       <c r="AB76" s="56"/>
       <c r="AC76" s="56"/>
       <c r="AD76" s="56"/>
@@ -14154,11 +14265,11 @@
       <c r="AO76" s="56"/>
       <c r="AP76" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ76" s="71">
         <f t="shared" si="4"/>
-        <v>21.684375000000003</v>
+        <v>21.635294117647064</v>
       </c>
       <c r="AR76" s="71">
         <f>IFERROR(VLOOKUP(A76,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14166,7 +14277,7 @@
       </c>
       <c r="AS76" s="71">
         <f t="shared" si="5"/>
-        <v>1.104127943045313</v>
+        <v>1.0550470606923739</v>
       </c>
     </row>
     <row r="77" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14248,7 +14359,9 @@
       <c r="Z77" s="56">
         <v>25.666666666666671</v>
       </c>
-      <c r="AA77" s="56"/>
+      <c r="AA77" s="56">
+        <v>23.666666666666671</v>
+      </c>
       <c r="AB77" s="56"/>
       <c r="AC77" s="56"/>
       <c r="AD77" s="56"/>
@@ -14265,11 +14378,11 @@
       <c r="AO77" s="56"/>
       <c r="AP77" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ77" s="71">
         <f t="shared" si="4"/>
-        <v>24.395833333333332</v>
+        <v>24.352941176470587</v>
       </c>
       <c r="AR77" s="71">
         <f>IFERROR(VLOOKUP(A77,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14277,7 +14390,7 @@
       </c>
       <c r="AS77" s="71">
         <f t="shared" si="5"/>
-        <v>1.6956374900444509</v>
+        <v>1.6527453331817057</v>
       </c>
     </row>
     <row r="78" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14351,11 +14464,15 @@
         <v>26.55</v>
       </c>
       <c r="X78" s="56">
-        <v>29.6</v>
+        <v>29.75</v>
       </c>
       <c r="Y78" s="56"/>
-      <c r="Z78" s="56"/>
-      <c r="AA78" s="56"/>
+      <c r="Z78" s="56">
+        <v>29.95</v>
+      </c>
+      <c r="AA78" s="56">
+        <v>32.549999999999997</v>
+      </c>
       <c r="AB78" s="56"/>
       <c r="AC78" s="56"/>
       <c r="AD78" s="56"/>
@@ -14372,19 +14489,19 @@
       <c r="AO78" s="56"/>
       <c r="AP78" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ78" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ78" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>29.715624999999999</v>
       </c>
       <c r="AR78" s="71">
         <f>IFERROR(VLOOKUP(A78,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.36125399000905</v>
       </c>
-      <c r="AS78" s="71" t="str">
+      <c r="AS78" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.3543710099909489</v>
       </c>
     </row>
     <row r="79" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -14682,7 +14799,9 @@
       <c r="Z81" s="56">
         <v>26.85</v>
       </c>
-      <c r="AA81" s="56"/>
+      <c r="AA81" s="56">
+        <v>24.85</v>
+      </c>
       <c r="AB81" s="56"/>
       <c r="AC81" s="56"/>
       <c r="AD81" s="56"/>
@@ -14699,7 +14818,7 @@
       <c r="AO81" s="56"/>
       <c r="AP81" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ81" s="71" t="str">
         <f t="shared" si="4"/>
@@ -14791,7 +14910,9 @@
       <c r="Z82" s="56">
         <v>29.13333333333334</v>
       </c>
-      <c r="AA82" s="56"/>
+      <c r="AA82" s="56">
+        <v>26.466666666666669</v>
+      </c>
       <c r="AB82" s="56"/>
       <c r="AC82" s="56"/>
       <c r="AD82" s="56"/>
@@ -14808,11 +14929,11 @@
       <c r="AO82" s="56"/>
       <c r="AP82" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ82" s="71">
         <f t="shared" si="4"/>
-        <v>27.837777777777781</v>
+        <v>27.752083333333339</v>
       </c>
       <c r="AR82" s="71">
         <f>IFERROR(VLOOKUP(A82,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -14820,7 +14941,7 @@
       </c>
       <c r="AS82" s="71">
         <f t="shared" si="5"/>
-        <v>1.2166026578168108</v>
+        <v>1.1309082133723685</v>
       </c>
     </row>
     <row r="83" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15053,8 +15174,12 @@
       <c r="Y85" s="56">
         <v>31.85</v>
       </c>
-      <c r="Z85" s="56"/>
-      <c r="AA85" s="56"/>
+      <c r="Z85" s="56">
+        <v>32.650000000000013</v>
+      </c>
+      <c r="AA85" s="56">
+        <v>32.049999999999997</v>
+      </c>
       <c r="AB85" s="56"/>
       <c r="AC85" s="56"/>
       <c r="AD85" s="56"/>
@@ -15071,11 +15196,11 @@
       <c r="AO85" s="56"/>
       <c r="AP85" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
-      </c>
-      <c r="AQ85" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ85" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>31.310000000000006</v>
       </c>
       <c r="AR85" s="71" t="str">
         <f>IFERROR(VLOOKUP(A85,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15165,7 +15290,9 @@
       <c r="Z86" s="56">
         <v>30.15</v>
       </c>
-      <c r="AA86" s="56"/>
+      <c r="AA86" s="56">
+        <v>28.75</v>
+      </c>
       <c r="AB86" s="56"/>
       <c r="AC86" s="56"/>
       <c r="AD86" s="56"/>
@@ -15182,11 +15309,11 @@
       <c r="AO86" s="56"/>
       <c r="AP86" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ86" s="71">
         <f t="shared" si="4"/>
-        <v>29.099999999999998</v>
+        <v>29.079411764705881</v>
       </c>
       <c r="AR86" s="71">
         <f>IFERROR(VLOOKUP(A86,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15194,7 +15321,7 @@
       </c>
       <c r="AS86" s="71">
         <f t="shared" si="5"/>
-        <v>1.7202719087205089</v>
+        <v>1.6996836734263923</v>
       </c>
     </row>
     <row r="87" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15268,7 +15395,9 @@
       <c r="Z87" s="56">
         <v>29.3</v>
       </c>
-      <c r="AA87" s="56"/>
+      <c r="AA87" s="56">
+        <v>28.15</v>
+      </c>
       <c r="AB87" s="56"/>
       <c r="AC87" s="56"/>
       <c r="AD87" s="56"/>
@@ -15285,7 +15414,7 @@
       <c r="AO87" s="56"/>
       <c r="AP87" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ87" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15379,7 +15508,9 @@
       <c r="Z88" s="56">
         <v>29.65</v>
       </c>
-      <c r="AA88" s="56"/>
+      <c r="AA88" s="56">
+        <v>27.8</v>
+      </c>
       <c r="AB88" s="56"/>
       <c r="AC88" s="56"/>
       <c r="AD88" s="56"/>
@@ -15396,11 +15527,11 @@
       <c r="AO88" s="56"/>
       <c r="AP88" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ88" s="71">
         <f t="shared" si="4"/>
-        <v>27.712499999999999</v>
+        <v>27.71764705882353</v>
       </c>
       <c r="AR88" s="71">
         <f>IFERROR(VLOOKUP(A88,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15408,7 +15539,7 @@
       </c>
       <c r="AS88" s="71">
         <f t="shared" si="5"/>
-        <v>0.64272102747909798</v>
+        <v>0.64786808630262982</v>
       </c>
     </row>
     <row r="89" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15488,7 +15619,9 @@
       <c r="Z89" s="56">
         <v>31.65</v>
       </c>
-      <c r="AA89" s="56"/>
+      <c r="AA89" s="56">
+        <v>28.3</v>
+      </c>
       <c r="AB89" s="56"/>
       <c r="AC89" s="56"/>
       <c r="AD89" s="56"/>
@@ -15505,11 +15638,11 @@
       <c r="AO89" s="56"/>
       <c r="AP89" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ89" s="71">
         <f t="shared" si="4"/>
-        <v>29.266666666666666</v>
+        <v>29.206250000000001</v>
       </c>
       <c r="AR89" s="71">
         <f>IFERROR(VLOOKUP(A89,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15517,7 +15650,7 @@
       </c>
       <c r="AS89" s="71">
         <f t="shared" si="5"/>
-        <v>1.5614573591713743</v>
+        <v>1.5010406925047093</v>
       </c>
     </row>
     <row r="90" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -15593,7 +15726,9 @@
       <c r="Z90" s="56">
         <v>29.75</v>
       </c>
-      <c r="AA90" s="56"/>
+      <c r="AA90" s="56">
+        <v>28.55</v>
+      </c>
       <c r="AB90" s="56"/>
       <c r="AC90" s="56"/>
       <c r="AD90" s="56"/>
@@ -15610,7 +15745,7 @@
       <c r="AO90" s="56"/>
       <c r="AP90" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ90" s="71" t="str">
         <f t="shared" si="4"/>
@@ -15918,7 +16053,9 @@
       <c r="Z93" s="56">
         <v>22.666666666666671</v>
       </c>
-      <c r="AA93" s="56"/>
+      <c r="AA93" s="56">
+        <v>22.93333333333333</v>
+      </c>
       <c r="AB93" s="56"/>
       <c r="AC93" s="56"/>
       <c r="AD93" s="56"/>
@@ -15935,11 +16072,11 @@
       <c r="AO93" s="56"/>
       <c r="AP93" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ93" s="71">
         <f t="shared" si="4"/>
-        <v>23.183333333333341</v>
+        <v>23.168627450980399</v>
       </c>
       <c r="AR93" s="71">
         <f>IFERROR(VLOOKUP(A93,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -15947,7 +16084,7 @@
       </c>
       <c r="AS93" s="71">
         <f t="shared" si="5"/>
-        <v>1.1934759362254717</v>
+        <v>1.1787700538725296</v>
       </c>
     </row>
     <row r="94" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16029,7 +16166,9 @@
       <c r="Z94" s="56">
         <v>15.5</v>
       </c>
-      <c r="AA94" s="56"/>
+      <c r="AA94" s="56">
+        <v>17.100000000000001</v>
+      </c>
       <c r="AB94" s="56"/>
       <c r="AC94" s="56"/>
       <c r="AD94" s="56"/>
@@ -16046,11 +16185,11 @@
       <c r="AO94" s="56"/>
       <c r="AP94" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ94" s="71">
         <f t="shared" si="4"/>
-        <v>17.071874999999999</v>
+        <v>17.073529411764707</v>
       </c>
       <c r="AR94" s="71">
         <f>IFERROR(VLOOKUP(A94,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16058,7 +16197,7 @@
       </c>
       <c r="AS94" s="71">
         <f t="shared" si="5"/>
-        <v>1.0320279801993379</v>
+        <v>1.0336823919640459</v>
       </c>
     </row>
     <row r="95" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16140,7 +16279,9 @@
       <c r="Z95" s="56">
         <v>16.100000000000001</v>
       </c>
-      <c r="AA95" s="56"/>
+      <c r="AA95" s="56">
+        <v>17.05</v>
+      </c>
       <c r="AB95" s="56"/>
       <c r="AC95" s="56"/>
       <c r="AD95" s="56"/>
@@ -16157,11 +16298,11 @@
       <c r="AO95" s="56"/>
       <c r="AP95" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ95" s="71">
         <f t="shared" si="4"/>
-        <v>15.868749999999999</v>
+        <v>15.938235294117646</v>
       </c>
       <c r="AR95" s="71">
         <f>IFERROR(VLOOKUP(A95,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16169,7 +16310,7 @@
       </c>
       <c r="AS95" s="71">
         <f t="shared" si="5"/>
-        <v>1.7454984660219193</v>
+        <v>1.8149837601395671</v>
       </c>
     </row>
     <row r="96" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16330,7 +16471,9 @@
       <c r="Z97" s="56">
         <v>15.95</v>
       </c>
-      <c r="AA97" s="56"/>
+      <c r="AA97" s="56">
+        <v>15.05</v>
+      </c>
       <c r="AB97" s="56"/>
       <c r="AC97" s="56"/>
       <c r="AD97" s="56"/>
@@ -16347,11 +16490,11 @@
       <c r="AO97" s="56"/>
       <c r="AP97" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ97" s="71">
         <f t="shared" si="4"/>
-        <v>16.831250000000001</v>
+        <v>16.726470588235294</v>
       </c>
       <c r="AR97" s="71">
         <f>IFERROR(VLOOKUP(A97,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16359,7 +16502,7 @@
       </c>
       <c r="AS97" s="71">
         <f t="shared" si="5"/>
-        <v>2.3866498012194803</v>
+        <v>2.2818703894547738</v>
       </c>
     </row>
     <row r="98" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16441,7 +16584,9 @@
       <c r="Z98" s="56">
         <v>13.8</v>
       </c>
-      <c r="AA98" s="56"/>
+      <c r="AA98" s="56">
+        <v>13.6</v>
+      </c>
       <c r="AB98" s="56"/>
       <c r="AC98" s="56"/>
       <c r="AD98" s="56"/>
@@ -16458,11 +16603,11 @@
       <c r="AO98" s="56"/>
       <c r="AP98" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ98" s="71">
         <f t="shared" si="4"/>
-        <v>14.096875000000002</v>
+        <v>14.067647058823532</v>
       </c>
       <c r="AR98" s="71" t="str">
         <f>IFERROR(VLOOKUP(A98,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16552,7 +16697,9 @@
       <c r="Z99" s="56">
         <v>14.866666666666671</v>
       </c>
-      <c r="AA99" s="56"/>
+      <c r="AA99" s="56">
+        <v>14.53333333333333</v>
+      </c>
       <c r="AB99" s="56"/>
       <c r="AC99" s="56"/>
       <c r="AD99" s="56"/>
@@ -16569,11 +16716,11 @@
       <c r="AO99" s="56"/>
       <c r="AP99" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ99" s="71">
         <f t="shared" si="4"/>
-        <v>14.731249999999999</v>
+        <v>14.719607843137254</v>
       </c>
       <c r="AR99" s="71" t="str">
         <f>IFERROR(VLOOKUP(A99,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16653,7 +16800,9 @@
       <c r="Z100" s="56">
         <v>17.266666666666669</v>
       </c>
-      <c r="AA100" s="56"/>
+      <c r="AA100" s="56">
+        <v>15.733333333333331</v>
+      </c>
       <c r="AB100" s="56"/>
       <c r="AC100" s="56"/>
       <c r="AD100" s="56"/>
@@ -16670,7 +16819,7 @@
       <c r="AO100" s="56"/>
       <c r="AP100" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ100" s="71" t="str">
         <f t="shared" si="4"/>
@@ -16764,7 +16913,9 @@
       <c r="Z101" s="56">
         <v>15.3</v>
       </c>
-      <c r="AA101" s="56"/>
+      <c r="AA101" s="56">
+        <v>14.95</v>
+      </c>
       <c r="AB101" s="56"/>
       <c r="AC101" s="56"/>
       <c r="AD101" s="56"/>
@@ -16781,11 +16932,11 @@
       <c r="AO101" s="56"/>
       <c r="AP101" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ101" s="71">
         <f t="shared" si="4"/>
-        <v>14.653125000000001</v>
+        <v>14.670588235294119</v>
       </c>
       <c r="AR101" s="71">
         <f>IFERROR(VLOOKUP(A101,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -16793,7 +16944,7 @@
       </c>
       <c r="AS101" s="71">
         <f t="shared" si="5"/>
-        <v>1.4051621649015704</v>
+        <v>1.4226254001956882</v>
       </c>
     </row>
     <row r="102" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -16867,7 +17018,9 @@
       <c r="Z102" s="56">
         <v>14.8</v>
       </c>
-      <c r="AA102" s="56"/>
+      <c r="AA102" s="56">
+        <v>14.866666666666671</v>
+      </c>
       <c r="AB102" s="56"/>
       <c r="AC102" s="56"/>
       <c r="AD102" s="56"/>
@@ -16884,7 +17037,7 @@
       <c r="AO102" s="56"/>
       <c r="AP102" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ102" s="71" t="str">
         <f t="shared" si="4"/>
@@ -17136,7 +17289,9 @@
       <c r="Z105" s="56">
         <v>20.399999999999999</v>
       </c>
-      <c r="AA105" s="56"/>
+      <c r="AA105" s="56">
+        <v>18.466666666666669</v>
+      </c>
       <c r="AB105" s="56"/>
       <c r="AC105" s="56"/>
       <c r="AD105" s="56"/>
@@ -17153,11 +17308,11 @@
       <c r="AO105" s="56"/>
       <c r="AP105" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ105" s="71">
         <f t="shared" si="4"/>
-        <v>18.608333333333334</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="AR105" s="71">
         <f>IFERROR(VLOOKUP(A105,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17165,7 +17320,7 @@
       </c>
       <c r="AS105" s="71">
         <f t="shared" si="5"/>
-        <v>1.5149741952777056</v>
+        <v>1.5066408619443727</v>
       </c>
     </row>
     <row r="106" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17245,7 +17400,9 @@
       <c r="Z106" s="56">
         <v>15.55</v>
       </c>
-      <c r="AA106" s="56"/>
+      <c r="AA106" s="56">
+        <v>13.25</v>
+      </c>
       <c r="AB106" s="56"/>
       <c r="AC106" s="56"/>
       <c r="AD106" s="56"/>
@@ -17262,11 +17419,11 @@
       <c r="AO106" s="56"/>
       <c r="AP106" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ106" s="71">
         <f t="shared" si="4"/>
-        <v>14.975</v>
+        <v>14.8671875</v>
       </c>
       <c r="AR106" s="71">
         <f>IFERROR(VLOOKUP(A106,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17274,7 +17431,7 @@
       </c>
       <c r="AS106" s="71">
         <f t="shared" si="5"/>
-        <v>0.90595170412746917</v>
+        <v>0.79813920412746953</v>
       </c>
     </row>
     <row r="107" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17435,7 +17592,9 @@
       <c r="Z108" s="56">
         <v>16.45</v>
       </c>
-      <c r="AA108" s="56"/>
+      <c r="AA108" s="56">
+        <v>14</v>
+      </c>
       <c r="AB108" s="56"/>
       <c r="AC108" s="56"/>
       <c r="AD108" s="56"/>
@@ -17452,11 +17611,11 @@
       <c r="AO108" s="56"/>
       <c r="AP108" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ108" s="71">
         <f t="shared" si="4"/>
-        <v>15.345312499999997</v>
+        <v>15.266176470588235</v>
       </c>
       <c r="AR108" s="71">
         <f>IFERROR(VLOOKUP(A108,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17464,7 +17623,7 @@
       </c>
       <c r="AS108" s="71">
         <f t="shared" si="5"/>
-        <v>0.66308984083022615</v>
+        <v>0.58395381141846414</v>
       </c>
     </row>
     <row r="109" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17546,7 +17705,9 @@
       <c r="Z109" s="56">
         <v>15.35</v>
       </c>
-      <c r="AA109" s="56"/>
+      <c r="AA109" s="56">
+        <v>16.3</v>
+      </c>
       <c r="AB109" s="56"/>
       <c r="AC109" s="56"/>
       <c r="AD109" s="56"/>
@@ -17563,11 +17724,11 @@
       <c r="AO109" s="56"/>
       <c r="AP109" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ109" s="71">
         <f t="shared" si="4"/>
-        <v>15.890625</v>
+        <v>15.914705882352942</v>
       </c>
       <c r="AR109" s="71">
         <f>IFERROR(VLOOKUP(A109,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17575,7 +17736,7 @@
       </c>
       <c r="AS109" s="71">
         <f t="shared" si="5"/>
-        <v>1.3085761849534396</v>
+        <v>1.332657067306382</v>
       </c>
     </row>
     <row r="110" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17657,7 +17818,9 @@
       <c r="Z110" s="56">
         <v>19.466666666666669</v>
       </c>
-      <c r="AA110" s="56"/>
+      <c r="AA110" s="56">
+        <v>19.133333333333329</v>
+      </c>
       <c r="AB110" s="56"/>
       <c r="AC110" s="56"/>
       <c r="AD110" s="56"/>
@@ -17674,11 +17837,11 @@
       <c r="AO110" s="56"/>
       <c r="AP110" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ110" s="71">
         <f t="shared" si="4"/>
-        <v>18.716666666666669</v>
+        <v>18.741176470588236</v>
       </c>
       <c r="AR110" s="71">
         <f>IFERROR(VLOOKUP(A110,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17686,7 +17849,7 @@
       </c>
       <c r="AS110" s="71">
         <f t="shared" si="5"/>
-        <v>0.67001418923676681</v>
+        <v>0.69452399315833446</v>
       </c>
     </row>
     <row r="111" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17768,7 +17931,9 @@
       <c r="Z111" s="56">
         <v>17.850000000000001</v>
       </c>
-      <c r="AA111" s="56"/>
+      <c r="AA111" s="56">
+        <v>16.55</v>
+      </c>
       <c r="AB111" s="56"/>
       <c r="AC111" s="56"/>
       <c r="AD111" s="56"/>
@@ -17785,11 +17950,11 @@
       <c r="AO111" s="56"/>
       <c r="AP111" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ111" s="71">
         <f t="shared" si="4"/>
-        <v>17.003124999999997</v>
+        <v>16.976470588235291</v>
       </c>
       <c r="AR111" s="71">
         <f>IFERROR(VLOOKUP(A111,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17797,7 +17962,7 @@
       </c>
       <c r="AS111" s="71">
         <f t="shared" si="5"/>
-        <v>0.64260000503280779</v>
+        <v>0.61594559326810128</v>
       </c>
     </row>
     <row r="112" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17879,7 +18044,9 @@
       <c r="Z112" s="56">
         <v>20.06666666666667</v>
       </c>
-      <c r="AA112" s="56"/>
+      <c r="AA112" s="56">
+        <v>18.86666666666666</v>
+      </c>
       <c r="AB112" s="56"/>
       <c r="AC112" s="56"/>
       <c r="AD112" s="56"/>
@@ -17896,11 +18063,11 @@
       <c r="AO112" s="56"/>
       <c r="AP112" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ112" s="71">
         <f t="shared" si="4"/>
-        <v>19.416666666666664</v>
+        <v>19.384313725490195</v>
       </c>
       <c r="AR112" s="71">
         <f>IFERROR(VLOOKUP(A112,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -17908,7 +18075,7 @@
       </c>
       <c r="AS112" s="71">
         <f t="shared" si="5"/>
-        <v>1.7822238242327657</v>
+        <v>1.7498708830562961</v>
       </c>
     </row>
     <row r="113" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17986,7 +18153,9 @@
       <c r="Z113" s="56">
         <v>21.333333333333329</v>
       </c>
-      <c r="AA113" s="56"/>
+      <c r="AA113" s="56">
+        <v>19.2</v>
+      </c>
       <c r="AB113" s="56"/>
       <c r="AC113" s="56"/>
       <c r="AD113" s="56"/>
@@ -18003,19 +18172,19 @@
       <c r="AO113" s="56"/>
       <c r="AP113" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ113" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ113" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>20.36</v>
       </c>
       <c r="AR113" s="71">
         <f>IFERROR(VLOOKUP(A113,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>18.982990988223222</v>
       </c>
-      <c r="AS113" s="71" t="str">
+      <c r="AS113" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.3770090117767779</v>
       </c>
     </row>
     <row r="114" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18196,7 +18365,9 @@
       <c r="Z115" s="56">
         <v>30</v>
       </c>
-      <c r="AA115" s="56"/>
+      <c r="AA115" s="56">
+        <v>25.35</v>
+      </c>
       <c r="AB115" s="56"/>
       <c r="AC115" s="56"/>
       <c r="AD115" s="56"/>
@@ -18213,11 +18384,11 @@
       <c r="AO115" s="56"/>
       <c r="AP115" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ115" s="71">
         <f t="shared" si="4"/>
-        <v>28.110937499999999</v>
+        <v>27.948529411764707</v>
       </c>
       <c r="AR115" s="71">
         <f>IFERROR(VLOOKUP(A115,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18225,7 +18396,7 @@
       </c>
       <c r="AS115" s="71">
         <f t="shared" si="5"/>
-        <v>0.62646169354841774</v>
+        <v>0.46405360531312567</v>
       </c>
     </row>
     <row r="116" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18307,7 +18478,9 @@
       <c r="Z116" s="56">
         <v>19.533333333333331</v>
       </c>
-      <c r="AA116" s="56"/>
+      <c r="AA116" s="56">
+        <v>19.86666666666666</v>
+      </c>
       <c r="AB116" s="56"/>
       <c r="AC116" s="56"/>
       <c r="AD116" s="56"/>
@@ -18324,11 +18497,11 @@
       <c r="AO116" s="56"/>
       <c r="AP116" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ116" s="71">
         <f t="shared" si="4"/>
-        <v>19.362500000000004</v>
+        <v>19.392156862745104</v>
       </c>
       <c r="AR116" s="71">
         <f>IFERROR(VLOOKUP(A116,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18336,7 +18509,7 @@
       </c>
       <c r="AS116" s="71">
         <f t="shared" si="5"/>
-        <v>0.23106075189961572</v>
+        <v>0.26071761464471521</v>
       </c>
     </row>
     <row r="117" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18414,7 +18587,9 @@
       <c r="Z117" s="56">
         <v>29.266666666666669</v>
       </c>
-      <c r="AA117" s="56"/>
+      <c r="AA117" s="56">
+        <v>24.6</v>
+      </c>
       <c r="AB117" s="56"/>
       <c r="AC117" s="56"/>
       <c r="AD117" s="56"/>
@@ -18431,19 +18606,19 @@
       <c r="AO117" s="56"/>
       <c r="AP117" s="58">
         <f t="shared" si="3"/>
-        <v>14</v>
-      </c>
-      <c r="AQ117" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ117" s="71">
         <f t="shared" si="4"/>
-        <v/>
+        <v>27.777777777777779</v>
       </c>
       <c r="AR117" s="71">
         <f>IFERROR(VLOOKUP(A117,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>26.59831004118276</v>
       </c>
-      <c r="AS117" s="71" t="str">
+      <c r="AS117" s="71">
         <f t="shared" si="5"/>
-        <v/>
+        <v>1.1794677365950186</v>
       </c>
     </row>
     <row r="118" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -18519,7 +18694,9 @@
       <c r="Z118" s="56">
         <v>30.4</v>
       </c>
-      <c r="AA118" s="56"/>
+      <c r="AA118" s="56">
+        <v>26.93333333333333</v>
+      </c>
       <c r="AB118" s="56"/>
       <c r="AC118" s="56"/>
       <c r="AD118" s="56"/>
@@ -18536,7 +18713,7 @@
       <c r="AO118" s="56"/>
       <c r="AP118" s="58">
         <f t="shared" si="3"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ118" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18622,7 +18799,9 @@
         <v>23.733333333333331</v>
       </c>
       <c r="Z119" s="56"/>
-      <c r="AA119" s="56"/>
+      <c r="AA119" s="56">
+        <v>23.93333333333333</v>
+      </c>
       <c r="AB119" s="56"/>
       <c r="AC119" s="56"/>
       <c r="AD119" s="56"/>
@@ -18639,7 +18818,7 @@
       <c r="AO119" s="56"/>
       <c r="AP119" s="58">
         <f t="shared" si="3"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ119" s="71" t="str">
         <f t="shared" si="4"/>
@@ -18905,7 +19084,9 @@
       <c r="Z122" s="56">
         <v>13.4</v>
       </c>
-      <c r="AA122" s="56"/>
+      <c r="AA122" s="56">
+        <v>10.4</v>
+      </c>
       <c r="AB122" s="56"/>
       <c r="AC122" s="56"/>
       <c r="AD122" s="56"/>
@@ -18922,11 +19103,11 @@
       <c r="AO122" s="56"/>
       <c r="AP122" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ122" s="71">
         <f t="shared" si="4"/>
-        <v>12.754166666666668</v>
+        <v>12.615686274509805</v>
       </c>
       <c r="AR122" s="71">
         <f>IFERROR(VLOOKUP(A122,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -18934,7 +19115,7 @@
       </c>
       <c r="AS122" s="71">
         <f t="shared" si="5"/>
-        <v>1.8978342385341378</v>
+        <v>1.7593538463772749</v>
       </c>
     </row>
     <row r="123" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19275,7 +19456,9 @@
         <v>13.866666666666671</v>
       </c>
       <c r="Z126" s="56"/>
-      <c r="AA126" s="56"/>
+      <c r="AA126" s="56">
+        <v>12.866666666666671</v>
+      </c>
       <c r="AB126" s="56"/>
       <c r="AC126" s="56"/>
       <c r="AD126" s="56"/>
@@ -19292,7 +19475,7 @@
       <c r="AO126" s="56"/>
       <c r="AP126" s="58">
         <f t="shared" si="3"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ126" s="71" t="str">
         <f t="shared" si="4"/>
@@ -19625,7 +19808,9 @@
       <c r="Z130" s="56">
         <v>15.33333333333333</v>
       </c>
-      <c r="AA130" s="56"/>
+      <c r="AA130" s="56">
+        <v>14.866666666666671</v>
+      </c>
       <c r="AB130" s="56"/>
       <c r="AC130" s="56"/>
       <c r="AD130" s="56"/>
@@ -19642,11 +19827,11 @@
       <c r="AO130" s="56"/>
       <c r="AP130" s="58">
         <f t="shared" si="3"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ130" s="71">
         <f t="shared" si="4"/>
-        <v>14.856249999999998</v>
+        <v>14.856862745098038</v>
       </c>
       <c r="AR130" s="71">
         <f>IFERROR(VLOOKUP(A130,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19654,7 +19839,7 @@
       </c>
       <c r="AS130" s="71">
         <f t="shared" si="5"/>
-        <v>1.0098599581545766</v>
+        <v>1.0104727032526171</v>
       </c>
     </row>
     <row r="131" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19734,7 +19919,9 @@
       <c r="Z131" s="56">
         <v>18.149999999999999</v>
       </c>
-      <c r="AA131" s="56"/>
+      <c r="AA131" s="56">
+        <v>17.55</v>
+      </c>
       <c r="AB131" s="56"/>
       <c r="AC131" s="56"/>
       <c r="AD131" s="56"/>
@@ -19751,11 +19938,11 @@
       <c r="AO131" s="56"/>
       <c r="AP131" s="58">
         <f t="shared" si="3"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ131" s="71">
         <f t="shared" si="4"/>
-        <v>17.346666666666668</v>
+        <v>17.359375</v>
       </c>
       <c r="AR131" s="71">
         <f>IFERROR(VLOOKUP(A131,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19763,7 +19950,7 @@
       </c>
       <c r="AS131" s="71">
         <f t="shared" si="5"/>
-        <v>0.79488707478870779</v>
+        <v>0.80759540812204023</v>
       </c>
     </row>
     <row r="132" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -19924,7 +20111,9 @@
       <c r="Z133" s="56">
         <v>14.133333333333329</v>
       </c>
-      <c r="AA133" s="56"/>
+      <c r="AA133" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AB133" s="56"/>
       <c r="AC133" s="56"/>
       <c r="AD133" s="56"/>
@@ -19941,11 +20130,11 @@
       <c r="AO133" s="56"/>
       <c r="AP133" s="58">
         <f t="shared" ref="AP133:AP196" si="6">COUNTIF(K133:AO133,"&gt;0")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ133" s="71">
         <f t="shared" ref="AQ133:AQ196" si="7">IF(AP133&gt;14,AVERAGE(K133:AO133),"")</f>
-        <v>14.424999999999997</v>
+        <v>14.435294117647056</v>
       </c>
       <c r="AR133" s="71">
         <f>IFERROR(VLOOKUP(A133,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -19953,7 +20142,7 @@
       </c>
       <c r="AS133" s="71">
         <f t="shared" ref="AS133:AS196" si="8">IF(OR(AQ133="",AR133=""),"",IFERROR(AQ133-AR133,""))</f>
-        <v>1.2867366960374476</v>
+        <v>1.2970308136845059</v>
       </c>
     </row>
     <row r="134" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20035,7 +20224,9 @@
       <c r="Z134" s="56">
         <v>18.466666666666669</v>
       </c>
-      <c r="AA134" s="56"/>
+      <c r="AA134" s="56">
+        <v>17.733333333333331</v>
+      </c>
       <c r="AB134" s="56"/>
       <c r="AC134" s="56"/>
       <c r="AD134" s="56"/>
@@ -20052,11 +20243,11 @@
       <c r="AO134" s="56"/>
       <c r="AP134" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ134" s="71">
         <f t="shared" si="7"/>
-        <v>18.029166666666669</v>
+        <v>18.011764705882356</v>
       </c>
       <c r="AR134" s="71">
         <f>IFERROR(VLOOKUP(A134,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20064,7 +20255,7 @@
       </c>
       <c r="AS134" s="71">
         <f t="shared" si="8"/>
-        <v>1.9053624038022896</v>
+        <v>1.8879604430179775</v>
       </c>
     </row>
     <row r="135" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20144,7 +20335,9 @@
       <c r="Z135" s="56">
         <v>18.600000000000001</v>
       </c>
-      <c r="AA135" s="56"/>
+      <c r="AA135" s="56">
+        <v>19.149999999999999</v>
+      </c>
       <c r="AB135" s="56"/>
       <c r="AC135" s="56"/>
       <c r="AD135" s="56"/>
@@ -20161,11 +20354,11 @@
       <c r="AO135" s="56"/>
       <c r="AP135" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ135" s="71">
         <f t="shared" si="7"/>
-        <v>18.439999999999998</v>
+        <v>18.484374999999996</v>
       </c>
       <c r="AR135" s="71">
         <f>IFERROR(VLOOKUP(A135,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20173,7 +20366,7 @@
       </c>
       <c r="AS135" s="71">
         <f t="shared" si="8"/>
-        <v>0.63657438805698874</v>
+        <v>0.68094938805698746</v>
       </c>
     </row>
     <row r="136" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20441,7 +20634,9 @@
       <c r="Z138" s="56">
         <v>21</v>
       </c>
-      <c r="AA138" s="56"/>
+      <c r="AA138" s="56">
+        <v>22.466666666666669</v>
+      </c>
       <c r="AB138" s="56"/>
       <c r="AC138" s="56"/>
       <c r="AD138" s="56"/>
@@ -20458,11 +20653,11 @@
       <c r="AO138" s="56"/>
       <c r="AP138" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ138" s="71">
         <f t="shared" si="7"/>
-        <v>21.43333333333333</v>
+        <v>21.494117647058822</v>
       </c>
       <c r="AR138" s="71">
         <f>IFERROR(VLOOKUP(A138,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20470,7 +20665,7 @@
       </c>
       <c r="AS138" s="71">
         <f t="shared" si="8"/>
-        <v>1.4377886427095987</v>
+        <v>1.4985729564350905</v>
       </c>
     </row>
     <row r="139" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20552,7 +20747,9 @@
       <c r="Z139" s="56">
         <v>14.35</v>
       </c>
-      <c r="AA139" s="56"/>
+      <c r="AA139" s="56">
+        <v>13.925000000000001</v>
+      </c>
       <c r="AB139" s="56"/>
       <c r="AC139" s="56"/>
       <c r="AD139" s="56"/>
@@ -20569,11 +20766,11 @@
       <c r="AO139" s="56"/>
       <c r="AP139" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ139" s="71">
         <f t="shared" si="7"/>
-        <v>14.445312499999998</v>
+        <v>14.414705882352941</v>
       </c>
       <c r="AR139" s="71">
         <f>IFERROR(VLOOKUP(A139,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20581,7 +20778,7 @@
       </c>
       <c r="AS139" s="71">
         <f t="shared" si="8"/>
-        <v>1.1930142784310682</v>
+        <v>1.1624076607840106</v>
       </c>
     </row>
     <row r="140" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20663,7 +20860,9 @@
       <c r="Z140" s="56">
         <v>15.85</v>
       </c>
-      <c r="AA140" s="56"/>
+      <c r="AA140" s="56">
+        <v>15.7</v>
+      </c>
       <c r="AB140" s="56"/>
       <c r="AC140" s="56"/>
       <c r="AD140" s="56"/>
@@ -20680,11 +20879,11 @@
       <c r="AO140" s="56"/>
       <c r="AP140" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ140" s="71">
         <f t="shared" si="7"/>
-        <v>16.162500000000001</v>
+        <v>16.13529411764706</v>
       </c>
       <c r="AR140" s="71">
         <f>IFERROR(VLOOKUP(A140,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20692,7 +20891,7 @@
       </c>
       <c r="AS140" s="71">
         <f t="shared" si="8"/>
-        <v>0.44456590656285222</v>
+        <v>0.41736002420991092</v>
       </c>
     </row>
     <row r="141" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20774,7 +20973,9 @@
       <c r="Z141" s="56">
         <v>13</v>
       </c>
-      <c r="AA141" s="56"/>
+      <c r="AA141" s="56">
+        <v>13.866666666666671</v>
+      </c>
       <c r="AB141" s="56"/>
       <c r="AC141" s="56"/>
       <c r="AD141" s="56"/>
@@ -20791,11 +20992,11 @@
       <c r="AO141" s="56"/>
       <c r="AP141" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ141" s="71">
         <f t="shared" si="7"/>
-        <v>14.079166666666669</v>
+        <v>14.06666666666667</v>
       </c>
       <c r="AR141" s="71">
         <f>IFERROR(VLOOKUP(A141,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20803,7 +21004,7 @@
       </c>
       <c r="AS141" s="71">
         <f t="shared" si="8"/>
-        <v>1.3184817610443584</v>
+        <v>1.3059817610443591</v>
       </c>
     </row>
     <row r="142" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -20885,7 +21086,9 @@
       <c r="Z142" s="56">
         <v>12</v>
       </c>
-      <c r="AA142" s="56"/>
+      <c r="AA142" s="56">
+        <v>12.15</v>
+      </c>
       <c r="AB142" s="56"/>
       <c r="AC142" s="56"/>
       <c r="AD142" s="56"/>
@@ -20902,11 +21105,11 @@
       <c r="AO142" s="56"/>
       <c r="AP142" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ142" s="71">
         <f t="shared" si="7"/>
-        <v>12.353125</v>
+        <v>12.341176470588236</v>
       </c>
       <c r="AR142" s="71">
         <f>IFERROR(VLOOKUP(A142,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -20914,7 +21117,7 @@
       </c>
       <c r="AS142" s="71">
         <f t="shared" si="8"/>
-        <v>1.15996540655898</v>
+        <v>1.1480168771472155</v>
       </c>
     </row>
     <row r="143" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21105,7 +21308,9 @@
       <c r="Z144" s="56">
         <v>17.8</v>
       </c>
-      <c r="AA144" s="56"/>
+      <c r="AA144" s="56">
+        <v>16.733333333333331</v>
+      </c>
       <c r="AB144" s="56"/>
       <c r="AC144" s="56"/>
       <c r="AD144" s="56"/>
@@ -21122,11 +21327,11 @@
       <c r="AO144" s="56"/>
       <c r="AP144" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ144" s="71">
         <f t="shared" si="7"/>
-        <v>17.095833333333331</v>
+        <v>17.074509803921568</v>
       </c>
       <c r="AR144" s="71">
         <f>IFERROR(VLOOKUP(A144,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21134,7 +21339,7 @@
       </c>
       <c r="AS144" s="71">
         <f t="shared" si="8"/>
-        <v>1.4067598077741916</v>
+        <v>1.3854362783624286</v>
       </c>
     </row>
     <row r="145" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21216,7 +21421,9 @@
       <c r="Z145" s="56">
         <v>21.4</v>
       </c>
-      <c r="AA145" s="56"/>
+      <c r="AA145" s="56">
+        <v>20.399999999999999</v>
+      </c>
       <c r="AB145" s="56"/>
       <c r="AC145" s="56"/>
       <c r="AD145" s="56"/>
@@ -21233,11 +21440,11 @@
       <c r="AO145" s="56"/>
       <c r="AP145" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ145" s="71">
         <f t="shared" si="7"/>
-        <v>20.683333333333334</v>
+        <v>20.666666666666664</v>
       </c>
       <c r="AR145" s="71">
         <f>IFERROR(VLOOKUP(A145,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21245,7 +21452,7 @@
       </c>
       <c r="AS145" s="71">
         <f t="shared" si="8"/>
-        <v>1.2633375656641945</v>
+        <v>1.2466708989975253</v>
       </c>
     </row>
     <row r="146" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21322,8 +21529,12 @@
       <c r="Y146" s="56">
         <v>30.86666666666666</v>
       </c>
-      <c r="Z146" s="56"/>
-      <c r="AA146" s="56"/>
+      <c r="Z146" s="56">
+        <v>31</v>
+      </c>
+      <c r="AA146" s="56">
+        <v>31.533333333333331</v>
+      </c>
       <c r="AB146" s="56"/>
       <c r="AC146" s="56"/>
       <c r="AD146" s="56"/>
@@ -21340,19 +21551,19 @@
       <c r="AO146" s="56"/>
       <c r="AP146" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ146" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ146" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>30.345833333333339</v>
       </c>
       <c r="AR146" s="71">
         <f>IFERROR(VLOOKUP(A146,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>28.23129393152885</v>
       </c>
-      <c r="AS146" s="71" t="str">
+      <c r="AS146" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>2.114539401804489</v>
       </c>
     </row>
     <row r="147" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21434,7 +21645,9 @@
       <c r="Z147" s="56">
         <v>26.8</v>
       </c>
-      <c r="AA147" s="56"/>
+      <c r="AA147" s="56">
+        <v>25.6</v>
+      </c>
       <c r="AB147" s="56"/>
       <c r="AC147" s="56"/>
       <c r="AD147" s="56"/>
@@ -21451,11 +21664,11 @@
       <c r="AO147" s="56"/>
       <c r="AP147" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ147" s="71">
         <f t="shared" si="7"/>
-        <v>25.787500000000001</v>
+        <v>25.776470588235298</v>
       </c>
       <c r="AR147" s="71">
         <f>IFERROR(VLOOKUP(A147,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21463,7 +21676,7 @@
       </c>
       <c r="AS147" s="71">
         <f t="shared" si="8"/>
-        <v>2.3516209410688731</v>
+        <v>2.3405915293041701</v>
       </c>
     </row>
     <row r="148" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -21545,7 +21758,9 @@
       <c r="Z148" s="56">
         <v>30.86666666666666</v>
       </c>
-      <c r="AA148" s="56"/>
+      <c r="AA148" s="56">
+        <v>29.333333333333329</v>
+      </c>
       <c r="AB148" s="56"/>
       <c r="AC148" s="56"/>
       <c r="AD148" s="56"/>
@@ -21562,11 +21777,11 @@
       <c r="AO148" s="56"/>
       <c r="AP148" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ148" s="71">
         <f t="shared" si="7"/>
-        <v>29.716666666666669</v>
+        <v>29.694117647058825</v>
       </c>
       <c r="AR148" s="71">
         <f>IFERROR(VLOOKUP(A148,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -21574,7 +21789,7 @@
       </c>
       <c r="AS148" s="71">
         <f t="shared" si="8"/>
-        <v>1.4468742997506396</v>
+        <v>1.4243252801427957</v>
       </c>
     </row>
     <row r="149" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22081,7 +22296,9 @@
       <c r="Z154" s="56">
         <v>20.25</v>
       </c>
-      <c r="AA154" s="56"/>
+      <c r="AA154" s="56">
+        <v>20.3</v>
+      </c>
       <c r="AB154" s="56"/>
       <c r="AC154" s="56"/>
       <c r="AD154" s="56"/>
@@ -22098,11 +22315,11 @@
       <c r="AO154" s="56"/>
       <c r="AP154" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ154" s="71">
         <f t="shared" si="7"/>
-        <v>19.971875000000001</v>
+        <v>19.991176470588236</v>
       </c>
       <c r="AR154" s="71">
         <f>IFERROR(VLOOKUP(A154,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22110,7 +22327,7 @@
       </c>
       <c r="AS154" s="71">
         <f t="shared" si="8"/>
-        <v>0.70641955567915105</v>
+        <v>0.72572102626738655</v>
       </c>
     </row>
     <row r="155" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22192,7 +22409,9 @@
       <c r="Z155" s="56">
         <v>26.666666666666671</v>
       </c>
-      <c r="AA155" s="56"/>
+      <c r="AA155" s="56">
+        <v>27</v>
+      </c>
       <c r="AB155" s="56"/>
       <c r="AC155" s="56"/>
       <c r="AD155" s="56"/>
@@ -22209,11 +22428,11 @@
       <c r="AO155" s="56"/>
       <c r="AP155" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ155" s="71">
         <f t="shared" si="7"/>
-        <v>27.637500000000003</v>
+        <v>27.6</v>
       </c>
       <c r="AR155" s="71">
         <f>IFERROR(VLOOKUP(A155,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22221,7 +22440,7 @@
       </c>
       <c r="AS155" s="71">
         <f t="shared" si="8"/>
-        <v>0.31013585739988159</v>
+        <v>0.27263585739988017</v>
       </c>
     </row>
     <row r="156" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22371,7 +22590,9 @@
       <c r="Y157" s="56">
         <v>29.266666666666669</v>
       </c>
-      <c r="Z157" s="56"/>
+      <c r="Z157" s="56">
+        <v>28.266666666666669</v>
+      </c>
       <c r="AA157" s="56"/>
       <c r="AB157" s="56"/>
       <c r="AC157" s="56"/>
@@ -22389,7 +22610,7 @@
       <c r="AO157" s="56"/>
       <c r="AP157" s="58">
         <f t="shared" si="6"/>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ157" s="71" t="str">
         <f t="shared" si="7"/>
@@ -22588,7 +22809,9 @@
       <c r="Z159" s="56">
         <v>21.266666666666669</v>
       </c>
-      <c r="AA159" s="56"/>
+      <c r="AA159" s="56">
+        <v>19.93333333333333</v>
+      </c>
       <c r="AB159" s="56"/>
       <c r="AC159" s="56"/>
       <c r="AD159" s="56"/>
@@ -22605,11 +22828,11 @@
       <c r="AO159" s="56"/>
       <c r="AP159" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ159" s="71">
         <f t="shared" si="7"/>
-        <v>20.45</v>
+        <v>20.419607843137253</v>
       </c>
       <c r="AR159" s="71">
         <f>IFERROR(VLOOKUP(A159,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22617,7 +22840,7 @@
       </c>
       <c r="AS159" s="71">
         <f t="shared" si="8"/>
-        <v>1.9427916414877195</v>
+        <v>1.9123994846249737</v>
       </c>
     </row>
     <row r="160" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22697,7 +22920,9 @@
       <c r="Z160" s="56">
         <v>27.466666666666669</v>
       </c>
-      <c r="AA160" s="56"/>
+      <c r="AA160" s="56">
+        <v>27.533333333333331</v>
+      </c>
       <c r="AB160" s="56"/>
       <c r="AC160" s="56"/>
       <c r="AD160" s="56"/>
@@ -22714,11 +22939,11 @@
       <c r="AO160" s="56"/>
       <c r="AP160" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ160" s="71">
         <f t="shared" si="7"/>
-        <v>27.004444444444449</v>
+        <v>27.037500000000001</v>
       </c>
       <c r="AR160" s="71" t="str">
         <f>IFERROR(VLOOKUP(A160,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22885,7 +23110,9 @@
         <v>29.333333333333329</v>
       </c>
       <c r="Z162" s="56"/>
-      <c r="AA162" s="56"/>
+      <c r="AA162" s="56">
+        <v>28.666666666666671</v>
+      </c>
       <c r="AB162" s="56"/>
       <c r="AC162" s="56"/>
       <c r="AD162" s="56"/>
@@ -22902,11 +23129,11 @@
       <c r="AO162" s="56"/>
       <c r="AP162" s="58">
         <f t="shared" si="6"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ162" s="71">
         <f t="shared" si="7"/>
-        <v>28.124444444444443</v>
+        <v>28.158333333333331</v>
       </c>
       <c r="AR162" s="71">
         <f>IFERROR(VLOOKUP(A162,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -22914,7 +23141,7 @@
       </c>
       <c r="AS162" s="71">
         <f t="shared" si="8"/>
-        <v>0.28424282553809377</v>
+        <v>0.31813171442698263</v>
       </c>
     </row>
     <row r="163" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -22996,7 +23223,9 @@
       <c r="Z163" s="56">
         <v>22</v>
       </c>
-      <c r="AA163" s="56"/>
+      <c r="AA163" s="56">
+        <v>21.333333333333329</v>
+      </c>
       <c r="AB163" s="56"/>
       <c r="AC163" s="56"/>
       <c r="AD163" s="56"/>
@@ -23013,11 +23242,11 @@
       <c r="AO163" s="56"/>
       <c r="AP163" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ163" s="71">
         <f t="shared" si="7"/>
-        <v>21.291666666666671</v>
+        <v>21.294117647058826</v>
       </c>
       <c r="AR163" s="71">
         <f>IFERROR(VLOOKUP(A163,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23025,7 +23254,7 @@
       </c>
       <c r="AS163" s="71">
         <f t="shared" si="8"/>
-        <v>0.14135241277052302</v>
+        <v>0.14380339316267765</v>
       </c>
     </row>
     <row r="164" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23107,7 +23336,9 @@
       <c r="Z164" s="56">
         <v>26.15</v>
       </c>
-      <c r="AA164" s="56"/>
+      <c r="AA164" s="56">
+        <v>24.95</v>
+      </c>
       <c r="AB164" s="56"/>
       <c r="AC164" s="56"/>
       <c r="AD164" s="56"/>
@@ -23124,11 +23355,11 @@
       <c r="AO164" s="56"/>
       <c r="AP164" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ164" s="71">
         <f t="shared" si="7"/>
-        <v>25.090625000000003</v>
+        <v>25.082352941176474</v>
       </c>
       <c r="AR164" s="71">
         <f>IFERROR(VLOOKUP(A164,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23136,7 +23367,7 @@
       </c>
       <c r="AS164" s="71">
         <f t="shared" si="8"/>
-        <v>1.2782943403353322</v>
+        <v>1.2700222815118032</v>
       </c>
     </row>
     <row r="165" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23297,7 +23528,9 @@
       <c r="Z166" s="56">
         <v>16.13333333333334</v>
       </c>
-      <c r="AA166" s="56"/>
+      <c r="AA166" s="56">
+        <v>14.6</v>
+      </c>
       <c r="AB166" s="56"/>
       <c r="AC166" s="56"/>
       <c r="AD166" s="56"/>
@@ -23314,11 +23547,11 @@
       <c r="AO166" s="56"/>
       <c r="AP166" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ166" s="71">
         <f t="shared" si="7"/>
-        <v>14.704166666666666</v>
+        <v>14.698039215686274</v>
       </c>
       <c r="AR166" s="71">
         <f>IFERROR(VLOOKUP(A166,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23326,7 +23559,7 @@
       </c>
       <c r="AS166" s="71">
         <f t="shared" si="8"/>
-        <v>1.2570038932147156</v>
+        <v>1.2508764422343237</v>
       </c>
     </row>
     <row r="167" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23408,7 +23641,9 @@
       <c r="Z167" s="56">
         <v>20.8</v>
       </c>
-      <c r="AA167" s="56"/>
+      <c r="AA167" s="56">
+        <v>19.866666666666671</v>
+      </c>
       <c r="AB167" s="56"/>
       <c r="AC167" s="56"/>
       <c r="AD167" s="56"/>
@@ -23425,11 +23660,11 @@
       <c r="AO167" s="56"/>
       <c r="AP167" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ167" s="71">
         <f t="shared" si="7"/>
-        <v>20.112499999999994</v>
+        <v>20.098039215686271</v>
       </c>
       <c r="AR167" s="71">
         <f>IFERROR(VLOOKUP(A167,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23437,7 +23672,7 @@
       </c>
       <c r="AS167" s="71">
         <f t="shared" si="8"/>
-        <v>1.4274478318948844</v>
+        <v>1.4129870475811614</v>
       </c>
     </row>
     <row r="168" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23519,7 +23754,9 @@
       <c r="Z168" s="56">
         <v>28.55</v>
       </c>
-      <c r="AA168" s="56"/>
+      <c r="AA168" s="56">
+        <v>27.7</v>
+      </c>
       <c r="AB168" s="56"/>
       <c r="AC168" s="56"/>
       <c r="AD168" s="56"/>
@@ -23536,11 +23773,11 @@
       <c r="AO168" s="56"/>
       <c r="AP168" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ168" s="71">
         <f t="shared" si="7"/>
-        <v>27.340624999999999</v>
+        <v>27.361764705882351</v>
       </c>
       <c r="AR168" s="71">
         <f>IFERROR(VLOOKUP(A168,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23548,7 +23785,7 @@
       </c>
       <c r="AS168" s="71">
         <f t="shared" si="8"/>
-        <v>1.6553567184560691</v>
+        <v>1.6764964243384206</v>
       </c>
     </row>
     <row r="169" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23630,7 +23867,9 @@
       <c r="Z169" s="56">
         <v>10.5</v>
       </c>
-      <c r="AA169" s="56"/>
+      <c r="AA169" s="56">
+        <v>11.25</v>
+      </c>
       <c r="AB169" s="56"/>
       <c r="AC169" s="56"/>
       <c r="AD169" s="56"/>
@@ -23647,11 +23886,11 @@
       <c r="AO169" s="56"/>
       <c r="AP169" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ169" s="71">
         <f t="shared" si="7"/>
-        <v>10.5625</v>
+        <v>10.602941176470589</v>
       </c>
       <c r="AR169" s="71">
         <f>IFERROR(VLOOKUP(A169,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23659,7 +23898,7 @@
       </c>
       <c r="AS169" s="71">
         <f t="shared" si="8"/>
-        <v>1.3841271520648082</v>
+        <v>1.4245683285353969</v>
       </c>
     </row>
     <row r="170" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -23733,7 +23972,9 @@
       <c r="Z170" s="56">
         <v>28.06666666666667</v>
       </c>
-      <c r="AA170" s="56"/>
+      <c r="AA170" s="56">
+        <v>25.2</v>
+      </c>
       <c r="AB170" s="56"/>
       <c r="AC170" s="56"/>
       <c r="AD170" s="56"/>
@@ -23750,7 +23991,7 @@
       <c r="AO170" s="56"/>
       <c r="AP170" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ170" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23838,7 +24079,9 @@
       <c r="Z171" s="56">
         <v>20.06666666666667</v>
       </c>
-      <c r="AA171" s="56"/>
+      <c r="AA171" s="56">
+        <v>20</v>
+      </c>
       <c r="AB171" s="56"/>
       <c r="AC171" s="56"/>
       <c r="AD171" s="56"/>
@@ -23855,7 +24098,7 @@
       <c r="AO171" s="56"/>
       <c r="AP171" s="58">
         <f t="shared" si="6"/>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ171" s="71" t="str">
         <f t="shared" si="7"/>
@@ -23949,7 +24192,9 @@
       <c r="Z172" s="56">
         <v>24.6</v>
       </c>
-      <c r="AA172" s="56"/>
+      <c r="AA172" s="56">
+        <v>26.2</v>
+      </c>
       <c r="AB172" s="56"/>
       <c r="AC172" s="56"/>
       <c r="AD172" s="56"/>
@@ -23966,11 +24211,11 @@
       <c r="AO172" s="56"/>
       <c r="AP172" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ172" s="71">
         <f t="shared" si="7"/>
-        <v>25.043750000000003</v>
+        <v>25.111764705882354</v>
       </c>
       <c r="AR172" s="71">
         <f>IFERROR(VLOOKUP(A172,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -23978,7 +24223,7 @@
       </c>
       <c r="AS172" s="71">
         <f t="shared" si="8"/>
-        <v>0.99348736294831141</v>
+        <v>1.0615020688306629</v>
       </c>
     </row>
     <row r="173" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24060,7 +24305,9 @@
       <c r="Z173" s="56">
         <v>23.65</v>
       </c>
-      <c r="AA173" s="56"/>
+      <c r="AA173" s="56">
+        <v>25.15</v>
+      </c>
       <c r="AB173" s="56"/>
       <c r="AC173" s="56"/>
       <c r="AD173" s="56"/>
@@ -24077,11 +24324,11 @@
       <c r="AO173" s="56"/>
       <c r="AP173" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ173" s="71">
         <f t="shared" si="7"/>
-        <v>23.849999999999998</v>
+        <v>23.92647058823529</v>
       </c>
       <c r="AR173" s="71">
         <f>IFERROR(VLOOKUP(A173,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24089,7 +24336,7 @@
       </c>
       <c r="AS173" s="71">
         <f t="shared" si="8"/>
-        <v>0.35214677012055873</v>
+        <v>0.4286173583558508</v>
       </c>
     </row>
     <row r="174" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24238,11 +24485,19 @@
       <c r="V175" s="56">
         <v>22.13333333333334</v>
       </c>
-      <c r="W175" s="56"/>
+      <c r="W175" s="56">
+        <v>23.6</v>
+      </c>
       <c r="X175" s="56"/>
-      <c r="Y175" s="56"/>
-      <c r="Z175" s="56"/>
-      <c r="AA175" s="56"/>
+      <c r="Y175" s="56">
+        <v>24.06666666666667</v>
+      </c>
+      <c r="Z175" s="56">
+        <v>22.6</v>
+      </c>
+      <c r="AA175" s="56">
+        <v>24.333333333333329</v>
+      </c>
       <c r="AB175" s="56"/>
       <c r="AC175" s="56"/>
       <c r="AD175" s="56"/>
@@ -24259,19 +24514,19 @@
       <c r="AO175" s="56"/>
       <c r="AP175" s="58">
         <f t="shared" si="6"/>
-        <v>12</v>
-      </c>
-      <c r="AQ175" s="71" t="str">
+        <v>16</v>
+      </c>
+      <c r="AQ175" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>23.604166666666664</v>
       </c>
       <c r="AR175" s="71">
         <f>IFERROR(VLOOKUP(A175,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>23.1422602484216</v>
       </c>
-      <c r="AS175" s="71" t="str">
+      <c r="AS175" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>0.46190641824506429</v>
       </c>
     </row>
     <row r="176" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24511,7 +24766,9 @@
       <c r="Z178" s="56">
         <v>23.933333333333341</v>
       </c>
-      <c r="AA178" s="56"/>
+      <c r="AA178" s="56">
+        <v>23.733333333333331</v>
+      </c>
       <c r="AB178" s="56"/>
       <c r="AC178" s="56"/>
       <c r="AD178" s="56"/>
@@ -24528,11 +24785,11 @@
       <c r="AO178" s="56"/>
       <c r="AP178" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ178" s="71">
         <f t="shared" si="7"/>
-        <v>24.383333333333336</v>
+        <v>24.345098039215689</v>
       </c>
       <c r="AR178" s="71">
         <f>IFERROR(VLOOKUP(A178,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24540,7 +24797,7 @@
       </c>
       <c r="AS178" s="71">
         <f t="shared" si="8"/>
-        <v>0.526846679780828</v>
+        <v>0.48861138566318019</v>
       </c>
     </row>
     <row r="179" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -24622,7 +24879,9 @@
       <c r="Z179" s="56">
         <v>16.55</v>
       </c>
-      <c r="AA179" s="56"/>
+      <c r="AA179" s="56">
+        <v>17.55</v>
+      </c>
       <c r="AB179" s="56"/>
       <c r="AC179" s="56"/>
       <c r="AD179" s="56"/>
@@ -24639,11 +24898,11 @@
       <c r="AO179" s="56"/>
       <c r="AP179" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ179" s="71">
         <f t="shared" si="7"/>
-        <v>17.746874999999999</v>
+        <v>17.735294117647058</v>
       </c>
       <c r="AR179" s="71">
         <f>IFERROR(VLOOKUP(A179,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -24651,7 +24910,7 @@
       </c>
       <c r="AS179" s="71">
         <f t="shared" si="8"/>
-        <v>0.98192814117883032</v>
+        <v>0.97034725882588901</v>
       </c>
     </row>
     <row r="180" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25075,7 +25334,9 @@
       <c r="Z184" s="56">
         <v>28.4</v>
       </c>
-      <c r="AA184" s="56"/>
+      <c r="AA184" s="56">
+        <v>28.933333333333341</v>
+      </c>
       <c r="AB184" s="56"/>
       <c r="AC184" s="56"/>
       <c r="AD184" s="56"/>
@@ -25092,11 +25353,11 @@
       <c r="AO184" s="56"/>
       <c r="AP184" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ184" s="71">
         <f t="shared" si="7"/>
-        <v>27.295833333333334</v>
+        <v>27.3921568627451</v>
       </c>
       <c r="AR184" s="71">
         <f>IFERROR(VLOOKUP(A184,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25104,7 +25365,7 @@
       </c>
       <c r="AS184" s="71">
         <f t="shared" si="8"/>
-        <v>1.1298191342707646</v>
+        <v>1.2261426636825306</v>
       </c>
     </row>
     <row r="185" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25453,7 +25714,9 @@
       <c r="Z188" s="56">
         <v>17.333333333333329</v>
       </c>
-      <c r="AA188" s="56"/>
+      <c r="AA188" s="56">
+        <v>17.466666666666669</v>
+      </c>
       <c r="AB188" s="56"/>
       <c r="AC188" s="56"/>
       <c r="AD188" s="56"/>
@@ -25470,11 +25733,11 @@
       <c r="AO188" s="56"/>
       <c r="AP188" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ188" s="71">
         <f t="shared" si="7"/>
-        <v>16.875</v>
+        <v>16.909803921568628</v>
       </c>
       <c r="AR188" s="71">
         <f>IFERROR(VLOOKUP(A188,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25482,7 +25745,7 @@
       </c>
       <c r="AS188" s="71">
         <f t="shared" si="8"/>
-        <v>1.2423188074782807</v>
+        <v>1.2771227290469085</v>
       </c>
     </row>
     <row r="189" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25665,7 +25928,9 @@
       <c r="Z190" s="56">
         <v>29.6</v>
       </c>
-      <c r="AA190" s="56"/>
+      <c r="AA190" s="56">
+        <v>29.93333333333333</v>
+      </c>
       <c r="AB190" s="56"/>
       <c r="AC190" s="56"/>
       <c r="AD190" s="56"/>
@@ -25682,11 +25947,11 @@
       <c r="AO190" s="56"/>
       <c r="AP190" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ190" s="71">
         <f t="shared" si="7"/>
-        <v>28.016666666666669</v>
+        <v>28.129411764705885</v>
       </c>
       <c r="AR190" s="71">
         <f>IFERROR(VLOOKUP(A190,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25694,7 +25959,7 @@
       </c>
       <c r="AS190" s="71">
         <f t="shared" si="8"/>
-        <v>-5.317222636431751E-3</v>
+        <v>0.10742787540278442</v>
       </c>
     </row>
     <row r="191" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -25881,7 +26146,9 @@
       <c r="Z192" s="56">
         <v>26.8</v>
       </c>
-      <c r="AA192" s="56"/>
+      <c r="AA192" s="56">
+        <v>26.4</v>
+      </c>
       <c r="AB192" s="56"/>
       <c r="AC192" s="56"/>
       <c r="AD192" s="56"/>
@@ -25898,11 +26165,11 @@
       <c r="AO192" s="56"/>
       <c r="AP192" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ192" s="71">
         <f t="shared" si="7"/>
-        <v>25.287500000000001</v>
+        <v>25.352941176470587</v>
       </c>
       <c r="AR192" s="71">
         <f>IFERROR(VLOOKUP(A192,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -25910,7 +26177,7 @@
       </c>
       <c r="AS192" s="71">
         <f t="shared" si="8"/>
-        <v>0.81531018404038136</v>
+        <v>0.88075136051096692</v>
       </c>
     </row>
     <row r="193" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26079,7 +26346,9 @@
       <c r="Z194" s="56">
         <v>21.666666666666671</v>
       </c>
-      <c r="AA194" s="56"/>
+      <c r="AA194" s="56">
+        <v>22.333333333333329</v>
+      </c>
       <c r="AB194" s="56"/>
       <c r="AC194" s="56"/>
       <c r="AD194" s="56"/>
@@ -26096,11 +26365,11 @@
       <c r="AO194" s="56"/>
       <c r="AP194" s="58">
         <f t="shared" si="6"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ194" s="71">
         <f t="shared" si="7"/>
-        <v>21.183333333333334</v>
+        <v>21.250980392156862</v>
       </c>
       <c r="AR194" s="71">
         <f>IFERROR(VLOOKUP(A194,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26108,7 +26377,7 @@
       </c>
       <c r="AS194" s="71">
         <f t="shared" si="8"/>
-        <v>-2.8777038853945669E-2</v>
+        <v>3.8870019969582614E-2</v>
       </c>
     </row>
     <row r="195" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26291,7 +26560,9 @@
       <c r="Z196" s="56">
         <v>20.466666666666669</v>
       </c>
-      <c r="AA196" s="56"/>
+      <c r="AA196" s="56">
+        <v>20.866666666666671</v>
+      </c>
       <c r="AB196" s="56"/>
       <c r="AC196" s="56"/>
       <c r="AD196" s="56"/>
@@ -26308,19 +26579,19 @@
       <c r="AO196" s="56"/>
       <c r="AP196" s="58">
         <f t="shared" si="6"/>
-        <v>14</v>
-      </c>
-      <c r="AQ196" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ196" s="71">
         <f t="shared" si="7"/>
-        <v/>
+        <v>20.415555555555557</v>
       </c>
       <c r="AR196" s="71">
         <f>IFERROR(VLOOKUP(A196,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
         <v>19.30020530053967</v>
       </c>
-      <c r="AS196" s="71" t="str">
+      <c r="AS196" s="71">
         <f t="shared" si="8"/>
-        <v/>
+        <v>1.1153502550158869</v>
       </c>
     </row>
     <row r="197" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26402,7 +26673,9 @@
       <c r="Z197" s="56">
         <v>26.8</v>
       </c>
-      <c r="AA197" s="56"/>
+      <c r="AA197" s="56">
+        <v>27.266666666666669</v>
+      </c>
       <c r="AB197" s="56"/>
       <c r="AC197" s="56"/>
       <c r="AD197" s="56"/>
@@ -26419,11 +26692,11 @@
       <c r="AO197" s="56"/>
       <c r="AP197" s="58">
         <f t="shared" ref="AP197:AP260" si="9">COUNTIF(K197:AO197,"&gt;0")</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ197" s="71">
         <f t="shared" ref="AQ197:AQ260" si="10">IF(AP197&gt;14,AVERAGE(K197:AO197),"")</f>
-        <v>25.641666666666662</v>
+        <v>25.737254901960778</v>
       </c>
       <c r="AR197" s="71">
         <f>IFERROR(VLOOKUP(A197,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26431,7 +26704,7 @@
       </c>
       <c r="AS197" s="71">
         <f t="shared" ref="AS197:AS260" si="11">IF(OR(AQ197="",AR197=""),"",IFERROR(AQ197-AR197,""))</f>
-        <v>1.5742754221327608</v>
+        <v>1.6698636574268768</v>
       </c>
     </row>
     <row r="198" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26513,7 +26786,9 @@
       <c r="Z198" s="56">
         <v>22.65</v>
       </c>
-      <c r="AA198" s="56"/>
+      <c r="AA198" s="56">
+        <v>21.75</v>
+      </c>
       <c r="AB198" s="56"/>
       <c r="AC198" s="56"/>
       <c r="AD198" s="56"/>
@@ -26530,11 +26805,11 @@
       <c r="AO198" s="56"/>
       <c r="AP198" s="58">
         <f t="shared" si="9"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ198" s="71">
         <f t="shared" si="10"/>
-        <v>21.821875000000002</v>
+        <v>21.817647058823532</v>
       </c>
       <c r="AR198" s="71" t="str">
         <f>IFERROR(VLOOKUP(A198,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26624,7 +26899,9 @@
       <c r="Z199" s="56">
         <v>17.06666666666667</v>
       </c>
-      <c r="AA199" s="56"/>
+      <c r="AA199" s="56">
+        <v>17</v>
+      </c>
       <c r="AB199" s="56"/>
       <c r="AC199" s="56"/>
       <c r="AD199" s="56"/>
@@ -26641,11 +26918,11 @@
       <c r="AO199" s="56"/>
       <c r="AP199" s="58">
         <f t="shared" si="9"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ199" s="71">
         <f t="shared" si="10"/>
-        <v>16.68333333333333</v>
+        <v>16.701960784313723</v>
       </c>
       <c r="AR199" s="71">
         <f>IFERROR(VLOOKUP(A199,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26653,7 +26930,7 @@
       </c>
       <c r="AS199" s="71">
         <f t="shared" si="11"/>
-        <v>0.6917605112721894</v>
+        <v>0.71038796225258238</v>
       </c>
     </row>
     <row r="200" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -26733,7 +27010,9 @@
       <c r="Z200" s="56">
         <v>15.3</v>
       </c>
-      <c r="AA200" s="56"/>
+      <c r="AA200" s="56">
+        <v>14.5</v>
+      </c>
       <c r="AB200" s="56"/>
       <c r="AC200" s="56"/>
       <c r="AD200" s="56"/>
@@ -26750,11 +27029,11 @@
       <c r="AO200" s="56"/>
       <c r="AP200" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ200" s="71">
         <f t="shared" si="10"/>
-        <v>15.016666666666667</v>
+        <v>14.984375</v>
       </c>
       <c r="AR200" s="71">
         <f>IFERROR(VLOOKUP(A200,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -26762,7 +27041,7 @@
       </c>
       <c r="AS200" s="71">
         <f t="shared" si="11"/>
-        <v>1.6370229726329182</v>
+        <v>1.6047313059662507</v>
       </c>
     </row>
     <row r="201" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27251,8 +27530,12 @@
       <c r="Y205" s="56">
         <v>15.45</v>
       </c>
-      <c r="Z205" s="56"/>
-      <c r="AA205" s="56"/>
+      <c r="Z205" s="56">
+        <v>14.1</v>
+      </c>
+      <c r="AA205" s="56">
+        <v>15.55</v>
+      </c>
       <c r="AB205" s="56"/>
       <c r="AC205" s="56"/>
       <c r="AD205" s="56"/>
@@ -27269,11 +27552,11 @@
       <c r="AO205" s="56"/>
       <c r="AP205" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ205" s="71">
         <f t="shared" si="10"/>
-        <v>15.550000000000002</v>
+        <v>15.464705882352943</v>
       </c>
       <c r="AR205" s="71">
         <f>IFERROR(VLOOKUP(A205,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27281,7 +27564,7 @@
       </c>
       <c r="AS205" s="71">
         <f t="shared" si="11"/>
-        <v>1.3034508746490818</v>
+        <v>1.2181567570020224</v>
       </c>
     </row>
     <row r="206" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -27569,7 +27852,9 @@
       <c r="Z208" s="56">
         <v>14.55</v>
       </c>
-      <c r="AA208" s="56"/>
+      <c r="AA208" s="56">
+        <v>15.2</v>
+      </c>
       <c r="AB208" s="56"/>
       <c r="AC208" s="56"/>
       <c r="AD208" s="56"/>
@@ -27586,11 +27871,11 @@
       <c r="AO208" s="56"/>
       <c r="AP208" s="58">
         <f t="shared" si="9"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ208" s="71">
         <f t="shared" si="10"/>
-        <v>15.43</v>
+        <v>15.415624999999999</v>
       </c>
       <c r="AR208" s="71" t="str">
         <f>IFERROR(VLOOKUP(A208,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -27680,7 +27965,9 @@
       <c r="Z209" s="56">
         <v>11.15</v>
       </c>
-      <c r="AA209" s="56"/>
+      <c r="AA209" s="56">
+        <v>11.3</v>
+      </c>
       <c r="AB209" s="56"/>
       <c r="AC209" s="56"/>
       <c r="AD209" s="56"/>
@@ -27697,11 +27984,11 @@
       <c r="AO209" s="56"/>
       <c r="AP209" s="58">
         <f t="shared" si="9"/>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ209" s="71">
         <f t="shared" si="10"/>
-        <v>11.053125000000001</v>
+        <v>11.067647058823532</v>
       </c>
       <c r="AR209" s="71" t="str">
         <f>IFERROR(VLOOKUP(A209,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
@@ -28005,7 +28292,9 @@
       <c r="Z212" s="56">
         <v>28</v>
       </c>
-      <c r="AA212" s="56"/>
+      <c r="AA212" s="56">
+        <v>27.85</v>
+      </c>
       <c r="AB212" s="56"/>
       <c r="AC212" s="56"/>
       <c r="AD212" s="56"/>
@@ -28022,11 +28311,11 @@
       <c r="AO212" s="56"/>
       <c r="AP212" s="58">
         <f t="shared" si="9"/>
-        <v>14</v>
-      </c>
-      <c r="AQ212" s="71" t="str">
+        <v>15</v>
+      </c>
+      <c r="AQ212" s="71">
         <f t="shared" si="10"/>
-        <v/>
+        <v>28.933333333333334</v>
       </c>
       <c r="AR212" s="71" t="str">
         <f>IFERROR(VLOOKUP(A212,Climatologia_TMED!A:U,9+$E$2,FALSE),"")</f>
